--- a/HN-C0626L1-Jv111+Jv113 [BC Java Backend] TKB Module 1_Programming Foundations.xlsx
+++ b/HN-C0626L1-Jv111+Jv113 [BC Java Backend] TKB Module 1_Programming Foundations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Code Gym\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFBD8D6F-E423-4DF4-B305-6FDE10FABCDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA0ACF2-1F97-4F5E-B87F-4ACD743FF540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1084" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="391">
   <si>
     <t>THỜI KHOÁ BIỂU MODULE</t>
   </si>
@@ -146,9 +146,6 @@
     <t>Buổi 6</t>
   </si>
   <si>
-    <t xml:space="preserve">Pseudo code &amp; Flowchart </t>
-  </si>
-  <si>
     <t>Buổi 7</t>
   </si>
   <si>
@@ -162,9 +159,6 @@
   </si>
   <si>
     <t>Buổi 9</t>
-  </si>
-  <si>
-    <t>Mini - Project 1</t>
   </si>
   <si>
     <t>Buổi 10</t>
@@ -1280,13 +1274,13 @@
     <t>Giới thiệu những điều cơ bản về HTML</t>
   </si>
   <si>
-    <t>Chưa học form vs table</t>
+    <t xml:space="preserve"> Câu lệnh điều kiện ( Tiếp)</t>
   </si>
   <si>
-    <t>Không có báo cáo nào cả</t>
+    <t>If else</t>
   </si>
   <si>
-    <t>Học form vs table</t>
+    <t>Swich case</t>
   </si>
 </sst>
 </file>
@@ -1788,7 +1782,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1978,9 +1972,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2002,13 +1993,13 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="19" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="19" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2458,11 +2449,11 @@
       <c r="A5" s="7"/>
       <c r="B5" s="1"/>
       <c r="C5" s="8"/>
-      <c r="D5" s="105" t="s">
-        <v>388</v>
-      </c>
-      <c r="E5" s="106" t="s">
-        <v>387</v>
+      <c r="D5" s="104" t="s">
+        <v>386</v>
+      </c>
+      <c r="E5" s="105" t="s">
+        <v>385</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
@@ -2490,10 +2481,10 @@
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="E6" s="113" t="s">
-        <v>382</v>
+        <v>381</v>
+      </c>
+      <c r="E6" s="110" t="s">
+        <v>380</v>
       </c>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
@@ -2555,7 +2546,7 @@
         <v>10</v>
       </c>
       <c r="E8" s="97" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F8" s="9"/>
       <c r="G8" s="9"/>
@@ -2672,10 +2663,10 @@
         <v>21</v>
       </c>
       <c r="F12" s="99" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G12" s="99" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -2709,10 +2700,10 @@
       <c r="E13" s="100" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="104" t="s">
-        <v>386</v>
-      </c>
-      <c r="G13" s="107"/>
+      <c r="F13" s="103" t="s">
+        <v>384</v>
+      </c>
+      <c r="G13" s="106"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -2744,10 +2735,10 @@
         <v>26</v>
       </c>
       <c r="E14" s="100"/>
-      <c r="F14" s="104" t="s">
-        <v>386</v>
-      </c>
-      <c r="G14" s="107"/>
+      <c r="F14" s="103" t="s">
+        <v>384</v>
+      </c>
+      <c r="G14" s="106"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -2779,10 +2770,10 @@
         <v>28</v>
       </c>
       <c r="E15" s="100"/>
-      <c r="F15" s="104" t="s">
-        <v>386</v>
-      </c>
-      <c r="G15" s="107"/>
+      <c r="F15" s="103" t="s">
+        <v>384</v>
+      </c>
+      <c r="G15" s="106"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -2813,15 +2804,11 @@
       <c r="D16" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="E16" s="100" t="s">
-        <v>31</v>
-      </c>
-      <c r="F16" s="104" t="s">
-        <v>386</v>
-      </c>
-      <c r="G16" s="110" t="s">
-        <v>391</v>
-      </c>
+      <c r="E16" s="100"/>
+      <c r="F16" s="103" t="s">
+        <v>384</v>
+      </c>
+      <c r="G16" s="109"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -2850,16 +2837,14 @@
         <v>Wed</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E17" s="100"/>
-      <c r="F17" s="104" t="s">
-        <v>386</v>
-      </c>
-      <c r="G17" s="110" t="s">
-        <v>390</v>
-      </c>
-      <c r="H17" s="109"/>
+      <c r="F17" s="103" t="s">
+        <v>384</v>
+      </c>
+      <c r="G17" s="109"/>
+      <c r="H17" s="108"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
@@ -2887,15 +2872,13 @@
         <v>Fri</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E18" s="100"/>
-      <c r="F18" s="104" t="s">
-        <v>386</v>
-      </c>
-      <c r="G18" s="110" t="s">
-        <v>392</v>
-      </c>
+      <c r="F18" s="103" t="s">
+        <v>384</v>
+      </c>
+      <c r="G18" s="109"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
@@ -2913,7 +2896,7 @@
     </row>
     <row r="19" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B19" s="19">
         <f>B18+3</f>
@@ -2924,15 +2907,13 @@
         <v>Mon</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="E19" s="100" t="s">
-        <v>31</v>
-      </c>
-      <c r="F19" s="104" t="s">
-        <v>386</v>
-      </c>
-      <c r="G19" s="107"/>
+        <v>35</v>
+      </c>
+      <c r="E19" s="100"/>
+      <c r="F19" s="103" t="s">
+        <v>384</v>
+      </c>
+      <c r="G19" s="109"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -2950,7 +2931,7 @@
     </row>
     <row r="20" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B20" s="19">
         <f t="shared" ref="B20:B21" si="2">B19+2</f>
@@ -2961,11 +2942,13 @@
         <v>Wed</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E20" s="100"/>
-      <c r="F20" s="102"/>
-      <c r="G20" s="107"/>
+      <c r="F20" s="103" t="s">
+        <v>384</v>
+      </c>
+      <c r="G20" s="106"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -2983,7 +2966,7 @@
     </row>
     <row r="21" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B21" s="19">
         <f t="shared" si="2"/>
@@ -2994,11 +2977,13 @@
         <v>Fri</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E21" s="100"/>
-      <c r="F21" s="102"/>
-      <c r="G21" s="107"/>
+      <c r="F21" s="103" t="s">
+        <v>384</v>
+      </c>
+      <c r="G21" s="106"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -3016,7 +3001,7 @@
     </row>
     <row r="22" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="18" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B22" s="19">
         <f>B21+3</f>
@@ -3027,13 +3012,15 @@
         <v>Mon</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="E22" s="100" t="s">
-        <v>31</v>
-      </c>
-      <c r="F22" s="102"/>
-      <c r="G22" s="107"/>
+        <v>44</v>
+      </c>
+      <c r="E22" s="100"/>
+      <c r="F22" s="103" t="s">
+        <v>384</v>
+      </c>
+      <c r="G22" s="109" t="s">
+        <v>389</v>
+      </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -3051,7 +3038,7 @@
     </row>
     <row r="23" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="18" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B23" s="19">
         <f t="shared" ref="B23:B24" si="3">B22+2</f>
@@ -3062,11 +3049,15 @@
         <v>Wed</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>44</v>
+        <v>388</v>
       </c>
       <c r="E23" s="100"/>
-      <c r="F23" s="102"/>
-      <c r="G23" s="107"/>
+      <c r="F23" s="103" t="s">
+        <v>384</v>
+      </c>
+      <c r="G23" s="109" t="s">
+        <v>390</v>
+      </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
@@ -3084,7 +3075,7 @@
     </row>
     <row r="24" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="18" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B24" s="19">
         <f t="shared" si="3"/>
@@ -3095,13 +3086,15 @@
         <v>Fri</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E24" s="100" t="s">
-        <v>47</v>
-      </c>
-      <c r="F24" s="103"/>
-      <c r="G24" s="107"/>
+        <v>45</v>
+      </c>
+      <c r="F24" s="103" t="s">
+        <v>384</v>
+      </c>
+      <c r="G24" s="106"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
@@ -3119,7 +3112,7 @@
     </row>
     <row r="25" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="18" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B25" s="19">
         <f>B24+3</f>
@@ -3130,13 +3123,15 @@
         <v>Mon</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E25" s="100" t="s">
         <v>31</v>
       </c>
-      <c r="F25" s="103"/>
-      <c r="G25" s="107"/>
+      <c r="F25" s="103" t="s">
+        <v>384</v>
+      </c>
+      <c r="G25" s="106"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
@@ -3154,7 +3149,7 @@
     </row>
     <row r="26" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="18" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B26" s="19">
         <f t="shared" ref="B26:B27" si="4">B25+2</f>
@@ -3165,11 +3160,11 @@
         <v>Wed</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E26" s="100"/>
       <c r="F26" s="102"/>
-      <c r="G26" s="107"/>
+      <c r="G26" s="106"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
@@ -3187,7 +3182,7 @@
     </row>
     <row r="27" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="18" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B27" s="19">
         <f t="shared" si="4"/>
@@ -3198,11 +3193,11 @@
         <v>Fri</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E27" s="100"/>
       <c r="F27" s="102"/>
-      <c r="G27" s="107"/>
+      <c r="G27" s="106"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
@@ -3220,7 +3215,7 @@
     </row>
     <row r="28" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="18" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B28" s="19">
         <f>B27+3</f>
@@ -3231,13 +3226,13 @@
         <v>Mon</v>
       </c>
       <c r="D28" s="20" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E28" s="100" t="s">
         <v>31</v>
       </c>
       <c r="F28" s="102"/>
-      <c r="G28" s="107"/>
+      <c r="G28" s="106"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
@@ -3255,7 +3250,7 @@
     </row>
     <row r="29" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="18" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B29" s="19">
         <f t="shared" ref="B29:B30" si="5">B28+2</f>
@@ -3266,11 +3261,11 @@
         <v>Wed</v>
       </c>
       <c r="D29" s="20" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E29" s="100"/>
       <c r="F29" s="102"/>
-      <c r="G29" s="107"/>
+      <c r="G29" s="106"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
@@ -3288,7 +3283,7 @@
     </row>
     <row r="30" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="18" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B30" s="19">
         <f t="shared" si="5"/>
@@ -3299,11 +3294,11 @@
         <v>Fri</v>
       </c>
       <c r="D30" s="20" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E30" s="100"/>
       <c r="F30" s="102"/>
-      <c r="G30" s="107"/>
+      <c r="G30" s="106"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
@@ -3321,7 +3316,7 @@
     </row>
     <row r="31" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="18" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B31" s="19">
         <f>B30+3</f>
@@ -3332,13 +3327,13 @@
         <v>Mon</v>
       </c>
       <c r="D31" s="20" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E31" s="100" t="s">
         <v>31</v>
       </c>
       <c r="F31" s="102"/>
-      <c r="G31" s="107"/>
+      <c r="G31" s="106"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
@@ -3356,7 +3351,7 @@
     </row>
     <row r="32" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="18" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B32" s="19">
         <f t="shared" ref="B32:B33" si="6">B31+2</f>
@@ -3367,11 +3362,11 @@
         <v>Wed</v>
       </c>
       <c r="D32" s="20" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E32" s="100"/>
       <c r="F32" s="102"/>
-      <c r="G32" s="107"/>
+      <c r="G32" s="106"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
@@ -3389,7 +3384,7 @@
     </row>
     <row r="33" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="18" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B33" s="19">
         <f t="shared" si="6"/>
@@ -3400,11 +3395,11 @@
         <v>Fri</v>
       </c>
       <c r="D33" s="20" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E33" s="100"/>
       <c r="F33" s="102"/>
-      <c r="G33" s="107"/>
+      <c r="G33" s="106"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
@@ -3422,7 +3417,7 @@
     </row>
     <row r="34" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="18" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B34" s="19">
         <f>B33+3</f>
@@ -3433,11 +3428,11 @@
         <v>Mon</v>
       </c>
       <c r="D34" s="20" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E34" s="100"/>
       <c r="F34" s="102"/>
-      <c r="G34" s="108"/>
+      <c r="G34" s="107"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
@@ -3455,7 +3450,7 @@
     </row>
     <row r="35" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="18" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B35" s="19">
         <f t="shared" ref="B35:B36" si="7">B34+2</f>
@@ -3466,13 +3461,13 @@
         <v>Wed</v>
       </c>
       <c r="D35" s="20" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E35" s="100" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F35" s="102"/>
-      <c r="G35" s="108"/>
+      <c r="G35" s="107"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
@@ -3490,7 +3485,7 @@
     </row>
     <row r="36" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="18" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B36" s="19">
         <f t="shared" si="7"/>
@@ -3501,13 +3496,13 @@
         <v>Fri</v>
       </c>
       <c r="D36" s="20" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E36" s="100" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F36" s="102"/>
-      <c r="G36" s="108"/>
+      <c r="G36" s="107"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
@@ -3525,7 +3520,7 @@
     </row>
     <row r="37" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="18" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B37" s="19">
         <f>B36+3</f>
@@ -3536,13 +3531,13 @@
         <v>Mon</v>
       </c>
       <c r="D37" s="20" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E37" s="100" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F37" s="102"/>
-      <c r="G37" s="107"/>
+      <c r="G37" s="106"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
@@ -3560,7 +3555,7 @@
     </row>
     <row r="38" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="18" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B38" s="19">
         <f t="shared" ref="B38:B39" si="8">B37+2</f>
@@ -3571,13 +3566,13 @@
         <v>Wed</v>
       </c>
       <c r="D38" s="20" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E38" s="100" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F38" s="102"/>
-      <c r="G38" s="107"/>
+      <c r="G38" s="106"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
@@ -3595,7 +3590,7 @@
     </row>
     <row r="39" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="18" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B39" s="19">
         <f t="shared" si="8"/>
@@ -3606,13 +3601,13 @@
         <v>Fri</v>
       </c>
       <c r="D39" s="20" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E39" s="101" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F39" s="102"/>
-      <c r="G39" s="107"/>
+      <c r="G39" s="106"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
@@ -3653,7 +3648,7 @@
     </row>
     <row r="41" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="21" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -25778,7 +25773,7 @@
       <c r="C2" s="26"/>
       <c r="D2" s="26"/>
       <c r="E2" s="27" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F2" s="28"/>
       <c r="G2" s="28"/>
@@ -25797,7 +25792,7 @@
       <c r="C3" s="26"/>
       <c r="D3" s="26"/>
       <c r="E3" s="29" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F3" s="26"/>
       <c r="G3" s="26"/>
@@ -25816,7 +25811,7 @@
       <c r="C4" s="26"/>
       <c r="D4" s="26"/>
       <c r="E4" s="31" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F4" s="26"/>
       <c r="G4" s="26"/>
@@ -25845,20 +25840,20 @@
     </row>
     <row r="6" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
       <c r="E6" s="32"/>
       <c r="F6" s="32"/>
       <c r="G6" s="34" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H6" s="35" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I6" s="32"/>
       <c r="L6" s="34"/>
@@ -25868,24 +25863,24 @@
     </row>
     <row r="7" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B7" s="111" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C7" s="112"/>
       <c r="D7" s="32" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F7" s="32"/>
       <c r="G7" s="34" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H7" s="35" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I7" s="32"/>
       <c r="J7" s="33"/>
@@ -25897,24 +25892,24 @@
     </row>
     <row r="8" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="32" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B8" s="111" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C8" s="112"/>
       <c r="D8" s="32" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F8" s="32"/>
       <c r="G8" s="32" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H8" s="35" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I8" s="32"/>
       <c r="J8" s="36"/>
@@ -25926,22 +25921,22 @@
     </row>
     <row r="9" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="32" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B9" s="111" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C9" s="112"/>
       <c r="D9" s="38"/>
       <c r="E9" s="33" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F9" s="36"/>
       <c r="G9" s="32" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H9" s="35" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I9" s="26"/>
       <c r="J9" s="26"/>
@@ -25953,24 +25948,24 @@
     </row>
     <row r="10" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B10" s="111" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C10" s="112"/>
       <c r="D10" s="32" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E10" s="36" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F10" s="26"/>
       <c r="G10" s="32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H10" s="33" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I10" s="26"/>
       <c r="J10" s="26"/>
@@ -26008,10 +26003,10 @@
     </row>
     <row r="12" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="40" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B12" s="41" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C12" s="41" t="s">
         <v>18</v>
@@ -26020,13 +26015,13 @@
         <v>19</v>
       </c>
       <c r="E12" s="42" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F12" s="42" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G12" s="43" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H12" s="26"/>
       <c r="I12" s="26"/>
@@ -26039,7 +26034,7 @@
     </row>
     <row r="13" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="44" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B13" s="45" t="s">
         <v>22</v>
@@ -26052,13 +26047,13 @@
         <v>Fri</v>
       </c>
       <c r="E13" s="47" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F13" s="47" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G13" s="48" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H13" s="26"/>
       <c r="I13" s="26"/>
@@ -26083,13 +26078,13 @@
         <v>Mon</v>
       </c>
       <c r="E14" s="26" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G14" s="50" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H14" s="26"/>
       <c r="I14" s="26"/>
@@ -26114,13 +26109,13 @@
         <v>Tue</v>
       </c>
       <c r="E15" s="26" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G15" s="50" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H15" s="26"/>
       <c r="I15" s="26"/>
@@ -26145,13 +26140,13 @@
         <v>Wed</v>
       </c>
       <c r="E16" s="26" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G16" s="50" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H16" s="26"/>
       <c r="I16" s="26"/>
@@ -26176,13 +26171,13 @@
         <v>Thu</v>
       </c>
       <c r="E17" s="53" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F17" s="53" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G17" s="54" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H17" s="26"/>
       <c r="I17" s="26"/>
@@ -26207,13 +26202,13 @@
         <v>Fri</v>
       </c>
       <c r="E18" s="47" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F18" s="47" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G18" s="48" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H18" s="26"/>
       <c r="I18" s="26"/>
@@ -26227,7 +26222,7 @@
     <row r="19" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="39"/>
       <c r="B19" s="39" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C19" s="49">
         <f t="shared" si="1"/>
@@ -26238,13 +26233,13 @@
         <v>Mon</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G19" s="50" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H19" s="26"/>
       <c r="I19" s="26"/>
@@ -26258,7 +26253,7 @@
     <row r="20" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="39"/>
       <c r="B20" s="39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C20" s="49">
         <f t="shared" si="1"/>
@@ -26269,13 +26264,13 @@
         <v>Tue</v>
       </c>
       <c r="E20" s="26" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G20" s="50" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H20" s="26"/>
       <c r="I20" s="26"/>
@@ -26289,7 +26284,7 @@
     <row r="21" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="39"/>
       <c r="B21" s="39" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C21" s="49">
         <f t="shared" si="1"/>
@@ -26300,13 +26295,13 @@
         <v>Wed</v>
       </c>
       <c r="E21" s="26" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G21" s="50" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H21" s="26"/>
       <c r="I21" s="26"/>
@@ -26320,7 +26315,7 @@
     <row r="22" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="39"/>
       <c r="B22" s="51" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C22" s="52">
         <f t="shared" si="1"/>
@@ -26331,13 +26326,13 @@
         <v>Thu</v>
       </c>
       <c r="E22" s="55" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F22" s="55" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G22" s="54" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H22" s="26"/>
       <c r="I22" s="26"/>
@@ -26351,7 +26346,7 @@
     <row r="23" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="39"/>
       <c r="B23" s="45" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C23" s="46">
         <f t="shared" si="1"/>
@@ -26362,13 +26357,13 @@
         <v>Fri</v>
       </c>
       <c r="E23" s="47" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F23" s="47" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G23" s="48" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H23" s="26"/>
       <c r="I23" s="26"/>
@@ -26382,7 +26377,7 @@
     <row r="24" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="39"/>
       <c r="B24" s="39" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C24" s="49">
         <f t="shared" si="1"/>
@@ -26393,13 +26388,13 @@
         <v>Mon</v>
       </c>
       <c r="E24" s="26" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G24" s="50" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H24" s="26"/>
       <c r="I24" s="26"/>
@@ -26413,7 +26408,7 @@
     <row r="25" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="39"/>
       <c r="B25" s="39" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C25" s="49">
         <f t="shared" si="1"/>
@@ -26424,13 +26419,13 @@
         <v>Tue</v>
       </c>
       <c r="E25" s="26" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G25" s="50" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H25" s="26"/>
       <c r="I25" s="26"/>
@@ -26444,7 +26439,7 @@
     <row r="26" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="39"/>
       <c r="B26" s="39" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C26" s="49">
         <f t="shared" si="1"/>
@@ -26455,13 +26450,13 @@
         <v>Wed</v>
       </c>
       <c r="E26" s="26" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F26" s="26" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G26" s="50" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H26" s="26"/>
       <c r="I26" s="26"/>
@@ -26475,7 +26470,7 @@
     <row r="27" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="39"/>
       <c r="B27" s="51" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C27" s="52">
         <f t="shared" si="1"/>
@@ -26486,13 +26481,13 @@
         <v>Thu</v>
       </c>
       <c r="E27" s="53" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F27" s="53" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G27" s="54" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H27" s="26"/>
       <c r="I27" s="26"/>
@@ -26506,7 +26501,7 @@
     <row r="28" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="39"/>
       <c r="B28" s="45" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C28" s="46">
         <f t="shared" si="1"/>
@@ -26517,13 +26512,13 @@
         <v>Fri</v>
       </c>
       <c r="E28" s="47" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F28" s="47" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G28" s="48" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H28" s="26"/>
       <c r="I28" s="26"/>
@@ -26537,7 +26532,7 @@
     <row r="29" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="39"/>
       <c r="B29" s="39" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C29" s="49">
         <f t="shared" si="1"/>
@@ -26548,13 +26543,13 @@
         <v>Mon</v>
       </c>
       <c r="E29" s="26" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F29" s="26" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G29" s="50" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H29" s="26"/>
       <c r="I29" s="26"/>
@@ -26568,7 +26563,7 @@
     <row r="30" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="39"/>
       <c r="B30" s="39" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C30" s="49">
         <f t="shared" si="1"/>
@@ -26579,13 +26574,13 @@
         <v>Tue</v>
       </c>
       <c r="E30" s="26" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G30" s="50" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H30" s="26"/>
       <c r="I30" s="26"/>
@@ -26599,7 +26594,7 @@
     <row r="31" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="39"/>
       <c r="B31" s="39" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C31" s="49">
         <f t="shared" si="1"/>
@@ -26610,13 +26605,13 @@
         <v>Wed</v>
       </c>
       <c r="E31" s="26" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F31" s="26" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G31" s="50" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H31" s="26"/>
       <c r="I31" s="26"/>
@@ -26630,7 +26625,7 @@
     <row r="32" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="39"/>
       <c r="B32" s="51" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C32" s="52">
         <f t="shared" si="1"/>
@@ -26641,13 +26636,13 @@
         <v>Thu</v>
       </c>
       <c r="E32" s="55" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F32" s="55" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G32" s="54" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H32" s="26"/>
       <c r="I32" s="26"/>
@@ -26661,7 +26656,7 @@
     <row r="33" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="39"/>
       <c r="B33" s="45" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C33" s="46">
         <f t="shared" si="1"/>
@@ -26672,13 +26667,13 @@
         <v>Fri</v>
       </c>
       <c r="E33" s="47" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F33" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G33" s="48" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H33" s="26"/>
       <c r="I33" s="26"/>
@@ -26692,7 +26687,7 @@
     <row r="34" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="39"/>
       <c r="B34" s="39" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C34" s="49">
         <f t="shared" si="1"/>
@@ -26703,13 +26698,13 @@
         <v>Mon</v>
       </c>
       <c r="E34" s="26" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F34" s="26" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G34" s="50" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H34" s="26"/>
       <c r="I34" s="26"/>
@@ -26723,7 +26718,7 @@
     <row r="35" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="39"/>
       <c r="B35" s="39" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C35" s="49">
         <f t="shared" si="1"/>
@@ -26734,13 +26729,13 @@
         <v>Tue</v>
       </c>
       <c r="E35" s="26" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F35" s="26" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G35" s="50" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H35" s="26"/>
       <c r="I35" s="26"/>
@@ -26754,7 +26749,7 @@
     <row r="36" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="39"/>
       <c r="B36" s="39" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C36" s="49">
         <f t="shared" si="1"/>
@@ -26765,13 +26760,13 @@
         <v>Wed</v>
       </c>
       <c r="E36" s="26" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F36" s="26" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G36" s="50" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H36" s="26"/>
       <c r="I36" s="26"/>
@@ -26785,7 +26780,7 @@
     <row r="37" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="39"/>
       <c r="B37" s="51" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C37" s="52">
         <f t="shared" si="1"/>
@@ -26796,13 +26791,13 @@
         <v>Thu</v>
       </c>
       <c r="E37" s="53" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F37" s="53" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G37" s="54" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H37" s="26"/>
       <c r="I37" s="26"/>
@@ -26816,7 +26811,7 @@
     <row r="38" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="39"/>
       <c r="B38" s="45" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C38" s="46">
         <f t="shared" si="1"/>
@@ -26827,13 +26822,13 @@
         <v>Fri</v>
       </c>
       <c r="E38" s="47" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F38" s="47" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G38" s="48" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H38" s="26"/>
       <c r="I38" s="26"/>
@@ -26847,7 +26842,7 @@
     <row r="39" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="39"/>
       <c r="B39" s="39" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C39" s="49">
         <f t="shared" si="1"/>
@@ -26858,13 +26853,13 @@
         <v>Mon</v>
       </c>
       <c r="E39" s="26" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F39" s="26" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G39" s="50" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H39" s="26"/>
       <c r="I39" s="26"/>
@@ -26878,7 +26873,7 @@
     <row r="40" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="39"/>
       <c r="B40" s="39" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C40" s="49">
         <f t="shared" si="1"/>
@@ -26889,13 +26884,13 @@
         <v>Tue</v>
       </c>
       <c r="E40" s="26" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F40" s="26" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G40" s="50" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H40" s="26"/>
       <c r="I40" s="26"/>
@@ -26909,7 +26904,7 @@
     <row r="41" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="39"/>
       <c r="B41" s="39" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C41" s="49">
         <f t="shared" si="1"/>
@@ -26920,13 +26915,13 @@
         <v>Wed</v>
       </c>
       <c r="E41" s="26" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F41" s="26" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G41" s="50" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H41" s="26"/>
       <c r="I41" s="26"/>
@@ -26940,7 +26935,7 @@
     <row r="42" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="39"/>
       <c r="B42" s="51" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C42" s="52">
         <f t="shared" si="1"/>
@@ -26951,13 +26946,13 @@
         <v>Thu</v>
       </c>
       <c r="E42" s="55" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F42" s="55" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G42" s="54" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H42" s="26"/>
       <c r="I42" s="26"/>
@@ -26971,7 +26966,7 @@
     <row r="43" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="39"/>
       <c r="B43" s="45" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C43" s="46">
         <f t="shared" si="1"/>
@@ -26982,13 +26977,13 @@
         <v>Fri</v>
       </c>
       <c r="E43" s="47" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F43" s="47" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G43" s="48" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="H43" s="26"/>
       <c r="I43" s="26"/>
@@ -27002,7 +26997,7 @@
     <row r="44" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="39"/>
       <c r="B44" s="39" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C44" s="49">
         <f t="shared" si="1"/>
@@ -27013,13 +27008,13 @@
         <v>Mon</v>
       </c>
       <c r="E44" s="26" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F44" s="26" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G44" s="50" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="H44" s="26"/>
       <c r="I44" s="26"/>
@@ -27033,7 +27028,7 @@
     <row r="45" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="39"/>
       <c r="B45" s="39" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C45" s="49">
         <f t="shared" si="1"/>
@@ -27044,13 +27039,13 @@
         <v>Tue</v>
       </c>
       <c r="E45" s="26" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F45" s="26" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G45" s="50" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H45" s="26"/>
       <c r="I45" s="26"/>
@@ -27064,7 +27059,7 @@
     <row r="46" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="39"/>
       <c r="B46" s="39" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C46" s="49">
         <f t="shared" si="1"/>
@@ -27075,13 +27070,13 @@
         <v>Wed</v>
       </c>
       <c r="E46" s="26" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F46" s="26" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G46" s="50" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H46" s="26"/>
       <c r="I46" s="26"/>
@@ -27095,7 +27090,7 @@
     <row r="47" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="39"/>
       <c r="B47" s="51" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C47" s="52">
         <f t="shared" si="1"/>
@@ -27106,13 +27101,13 @@
         <v>Thu</v>
       </c>
       <c r="E47" s="53" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F47" s="53" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G47" s="54" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H47" s="26"/>
       <c r="I47" s="26"/>
@@ -27126,7 +27121,7 @@
     <row r="48" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="39"/>
       <c r="B48" s="45" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C48" s="46">
         <f t="shared" si="1"/>
@@ -27137,13 +27132,13 @@
         <v>Fri</v>
       </c>
       <c r="E48" s="47" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F48" s="47" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G48" s="48" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H48" s="26"/>
       <c r="I48" s="26"/>
@@ -27157,7 +27152,7 @@
     <row r="49" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="39"/>
       <c r="B49" s="39" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C49" s="49">
         <f t="shared" si="1"/>
@@ -27168,13 +27163,13 @@
         <v>Mon</v>
       </c>
       <c r="E49" s="26" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F49" s="26" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G49" s="50" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H49" s="26"/>
       <c r="I49" s="26"/>
@@ -27188,7 +27183,7 @@
     <row r="50" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="39"/>
       <c r="B50" s="39" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C50" s="49">
         <f t="shared" si="1"/>
@@ -27199,13 +27194,13 @@
         <v>Tue</v>
       </c>
       <c r="E50" s="26" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F50" s="26" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G50" s="50" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H50" s="26"/>
       <c r="I50" s="26"/>
@@ -27219,7 +27214,7 @@
     <row r="51" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="39"/>
       <c r="B51" s="39" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C51" s="49">
         <f t="shared" si="1"/>
@@ -27230,13 +27225,13 @@
         <v>Wed</v>
       </c>
       <c r="E51" s="26" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F51" s="26" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G51" s="50" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H51" s="26"/>
       <c r="I51" s="26"/>
@@ -27250,7 +27245,7 @@
     <row r="52" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="39"/>
       <c r="B52" s="51" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C52" s="52">
         <f t="shared" si="1"/>
@@ -27261,13 +27256,13 @@
         <v>Thu</v>
       </c>
       <c r="E52" s="55" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F52" s="55" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G52" s="54" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H52" s="26"/>
       <c r="I52" s="26"/>
@@ -27281,7 +27276,7 @@
     <row r="53" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="39"/>
       <c r="B53" s="45" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C53" s="46">
         <f t="shared" si="1"/>
@@ -27292,13 +27287,13 @@
         <v>Fri</v>
       </c>
       <c r="E53" s="47" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F53" s="47" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G53" s="48" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H53" s="26"/>
       <c r="I53" s="26"/>
@@ -27312,7 +27307,7 @@
     <row r="54" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="39"/>
       <c r="B54" s="39" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C54" s="49">
         <f t="shared" si="1"/>
@@ -27323,13 +27318,13 @@
         <v>Mon</v>
       </c>
       <c r="E54" s="26" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F54" s="26" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G54" s="50" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H54" s="26"/>
       <c r="I54" s="26"/>
@@ -27343,7 +27338,7 @@
     <row r="55" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="39"/>
       <c r="B55" s="39" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C55" s="49">
         <f t="shared" si="1"/>
@@ -27354,13 +27349,13 @@
         <v>Tue</v>
       </c>
       <c r="E55" s="26" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F55" s="26" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G55" s="50" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H55" s="26"/>
       <c r="I55" s="26"/>
@@ -27374,7 +27369,7 @@
     <row r="56" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="39"/>
       <c r="B56" s="39" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C56" s="49">
         <f t="shared" si="1"/>
@@ -27385,13 +27380,13 @@
         <v>Wed</v>
       </c>
       <c r="E56" s="26" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F56" s="26" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G56" s="50" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H56" s="26"/>
       <c r="I56" s="26"/>
@@ -27405,7 +27400,7 @@
     <row r="57" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="39"/>
       <c r="B57" s="51" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C57" s="52">
         <f t="shared" si="1"/>
@@ -27416,13 +27411,13 @@
         <v>Thu</v>
       </c>
       <c r="E57" s="53" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F57" s="53" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G57" s="54" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H57" s="26"/>
       <c r="I57" s="26"/>
@@ -27436,7 +27431,7 @@
     <row r="58" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="39"/>
       <c r="B58" s="45" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C58" s="46">
         <f t="shared" si="1"/>
@@ -27447,13 +27442,13 @@
         <v>Fri</v>
       </c>
       <c r="E58" s="47" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F58" s="47" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G58" s="48" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H58" s="26"/>
       <c r="I58" s="26"/>
@@ -27467,7 +27462,7 @@
     <row r="59" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="39"/>
       <c r="B59" s="39" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C59" s="49">
         <f t="shared" si="1"/>
@@ -27478,13 +27473,13 @@
         <v>Mon</v>
       </c>
       <c r="E59" s="26" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F59" s="26" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G59" s="50" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H59" s="26"/>
       <c r="I59" s="26"/>
@@ -27498,7 +27493,7 @@
     <row r="60" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="39"/>
       <c r="B60" s="39" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C60" s="49">
         <f t="shared" si="1"/>
@@ -27509,13 +27504,13 @@
         <v>Tue</v>
       </c>
       <c r="E60" s="26" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F60" s="26" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G60" s="50" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H60" s="26"/>
       <c r="I60" s="26"/>
@@ -27529,7 +27524,7 @@
     <row r="61" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="39"/>
       <c r="B61" s="39" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C61" s="49">
         <f t="shared" si="1"/>
@@ -27540,13 +27535,13 @@
         <v>Wed</v>
       </c>
       <c r="E61" s="26" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F61" s="26" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G61" s="50" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H61" s="26"/>
       <c r="I61" s="26"/>
@@ -27560,7 +27555,7 @@
     <row r="62" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="39"/>
       <c r="B62" s="51" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C62" s="52">
         <f t="shared" si="1"/>
@@ -27571,13 +27566,13 @@
         <v>Thu</v>
       </c>
       <c r="E62" s="55" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F62" s="55" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G62" s="54" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H62" s="26"/>
       <c r="I62" s="26"/>
@@ -27591,7 +27586,7 @@
     <row r="63" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="51"/>
       <c r="B63" s="56" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C63" s="57">
         <f t="shared" si="1"/>
@@ -27602,10 +27597,10 @@
         <v>Fri</v>
       </c>
       <c r="E63" s="59" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F63" s="59" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G63" s="60"/>
       <c r="H63" s="26"/>
@@ -27619,10 +27614,10 @@
     </row>
     <row r="64" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="44" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B64" s="45" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C64" s="46">
         <f t="shared" si="1"/>
@@ -27633,13 +27628,13 @@
         <v>Mon</v>
       </c>
       <c r="E64" s="47" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F64" s="47" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G64" s="48" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="H64" s="26"/>
       <c r="I64" s="26"/>
@@ -27653,7 +27648,7 @@
     <row r="65" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="61"/>
       <c r="B65" s="39" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C65" s="49">
         <f t="shared" si="1"/>
@@ -27664,13 +27659,13 @@
         <v>Tue</v>
       </c>
       <c r="E65" s="26" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F65" s="26" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G65" s="50" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="H65" s="26"/>
       <c r="I65" s="26"/>
@@ -27684,7 +27679,7 @@
     <row r="66" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="61"/>
       <c r="B66" s="39" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C66" s="49">
         <f t="shared" si="1"/>
@@ -27695,13 +27690,13 @@
         <v>Wed</v>
       </c>
       <c r="E66" s="26" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F66" s="26" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G66" s="50" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H66" s="26"/>
       <c r="I66" s="26"/>
@@ -27715,7 +27710,7 @@
     <row r="67" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="61"/>
       <c r="B67" s="39" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C67" s="49">
         <f t="shared" si="1"/>
@@ -27726,13 +27721,13 @@
         <v>Thu</v>
       </c>
       <c r="E67" s="26" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F67" s="26" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G67" s="50" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H67" s="26"/>
       <c r="I67" s="26"/>
@@ -27746,7 +27741,7 @@
     <row r="68" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="61"/>
       <c r="B68" s="51" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C68" s="52">
         <f t="shared" si="1"/>
@@ -27757,13 +27752,13 @@
         <v>Fri</v>
       </c>
       <c r="E68" s="53" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F68" s="53" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G68" s="54" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H68" s="26"/>
       <c r="I68" s="26"/>
@@ -27777,7 +27772,7 @@
     <row r="69" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="62"/>
       <c r="B69" s="45" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C69" s="46">
         <f t="shared" si="1"/>
@@ -27788,13 +27783,13 @@
         <v>Mon</v>
       </c>
       <c r="E69" s="47" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F69" s="47" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G69" s="48" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H69" s="26"/>
       <c r="I69" s="26"/>
@@ -27808,7 +27803,7 @@
     <row r="70" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="39"/>
       <c r="B70" s="39" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C70" s="49">
         <f t="shared" si="1"/>
@@ -27819,13 +27814,13 @@
         <v>Tue</v>
       </c>
       <c r="E70" s="26" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F70" s="26" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G70" s="50" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="H70" s="26"/>
       <c r="I70" s="26"/>
@@ -27839,7 +27834,7 @@
     <row r="71" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="39"/>
       <c r="B71" s="39" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C71" s="49">
         <f t="shared" si="1"/>
@@ -27850,13 +27845,13 @@
         <v>Wed</v>
       </c>
       <c r="E71" s="26" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F71" s="26" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G71" s="50" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="H71" s="26"/>
       <c r="I71" s="26"/>
@@ -27870,7 +27865,7 @@
     <row r="72" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="39"/>
       <c r="B72" s="39" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C72" s="49">
         <f t="shared" si="1"/>
@@ -27881,13 +27876,13 @@
         <v>Thu</v>
       </c>
       <c r="E72" s="26" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F72" s="26" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G72" s="50" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H72" s="26"/>
       <c r="I72" s="26"/>
@@ -27901,7 +27896,7 @@
     <row r="73" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="39"/>
       <c r="B73" s="51" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C73" s="52">
         <f t="shared" si="1"/>
@@ -27912,13 +27907,13 @@
         <v>Fri</v>
       </c>
       <c r="E73" s="55" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F73" s="55" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="G73" s="54" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H73" s="26"/>
       <c r="I73" s="26"/>
@@ -27932,7 +27927,7 @@
     <row r="74" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="39"/>
       <c r="B74" s="45" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C74" s="46">
         <f t="shared" si="1"/>
@@ -27943,13 +27938,13 @@
         <v>Mon</v>
       </c>
       <c r="E74" s="47" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F74" s="47" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G74" s="48" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H74" s="26"/>
       <c r="I74" s="26"/>
@@ -27963,7 +27958,7 @@
     <row r="75" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="39"/>
       <c r="B75" s="39" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C75" s="49">
         <f t="shared" si="1"/>
@@ -27974,13 +27969,13 @@
         <v>Tue</v>
       </c>
       <c r="E75" s="26" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F75" s="26" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G75" s="50" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H75" s="26"/>
       <c r="I75" s="26"/>
@@ -27994,7 +27989,7 @@
     <row r="76" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="39"/>
       <c r="B76" s="39" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C76" s="49">
         <f t="shared" si="1"/>
@@ -28005,13 +28000,13 @@
         <v>Wed</v>
       </c>
       <c r="E76" s="26" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F76" s="26" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G76" s="50" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="H76" s="26"/>
       <c r="I76" s="26"/>
@@ -28025,7 +28020,7 @@
     <row r="77" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="39"/>
       <c r="B77" s="39" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C77" s="49">
         <f t="shared" si="1"/>
@@ -28036,13 +28031,13 @@
         <v>Thu</v>
       </c>
       <c r="E77" s="26" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F77" s="26" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G77" s="50" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="H77" s="26"/>
       <c r="I77" s="26"/>
@@ -28056,7 +28051,7 @@
     <row r="78" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="39"/>
       <c r="B78" s="51" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C78" s="52">
         <f t="shared" si="1"/>
@@ -28067,13 +28062,13 @@
         <v>Fri</v>
       </c>
       <c r="E78" s="53" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F78" s="53" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G78" s="54" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H78" s="26"/>
       <c r="I78" s="26"/>
@@ -28087,7 +28082,7 @@
     <row r="79" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="39"/>
       <c r="B79" s="45" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C79" s="46">
         <f t="shared" si="1"/>
@@ -28098,13 +28093,13 @@
         <v>Mon</v>
       </c>
       <c r="E79" s="47" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F79" s="47" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G79" s="48" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H79" s="26"/>
       <c r="I79" s="26"/>
@@ -28118,7 +28113,7 @@
     <row r="80" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="39"/>
       <c r="B80" s="39" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C80" s="49">
         <f t="shared" si="1"/>
@@ -28129,13 +28124,13 @@
         <v>Tue</v>
       </c>
       <c r="E80" s="26" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F80" s="26" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G80" s="50" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="H80" s="26"/>
       <c r="I80" s="26"/>
@@ -28149,7 +28144,7 @@
     <row r="81" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="39"/>
       <c r="B81" s="39" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C81" s="49">
         <f t="shared" si="1"/>
@@ -28160,13 +28155,13 @@
         <v>Wed</v>
       </c>
       <c r="E81" s="26" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F81" s="26" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G81" s="50" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="H81" s="26"/>
       <c r="I81" s="26"/>
@@ -28180,7 +28175,7 @@
     <row r="82" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="39"/>
       <c r="B82" s="39" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C82" s="49">
         <f t="shared" si="1"/>
@@ -28191,13 +28186,13 @@
         <v>Thu</v>
       </c>
       <c r="E82" s="26" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F82" s="26" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="G82" s="50" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="H82" s="26"/>
       <c r="I82" s="26"/>
@@ -28211,7 +28206,7 @@
     <row r="83" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="39"/>
       <c r="B83" s="51" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C83" s="52">
         <f t="shared" si="1"/>
@@ -28222,13 +28217,13 @@
         <v>Fri</v>
       </c>
       <c r="E83" s="55" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F83" s="55" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G83" s="54" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="H83" s="26"/>
       <c r="I83" s="26"/>
@@ -28242,7 +28237,7 @@
     <row r="84" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="51"/>
       <c r="B84" s="56" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C84" s="57">
         <f t="shared" si="1"/>
@@ -28253,10 +28248,10 @@
         <v>Mon</v>
       </c>
       <c r="E84" s="59" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F84" s="59" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G84" s="60"/>
       <c r="H84" s="26"/>
@@ -28270,10 +28265,10 @@
     </row>
     <row r="85" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="61" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B85" s="45" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C85" s="46">
         <f t="shared" si="1"/>
@@ -28284,13 +28279,13 @@
         <v>Tue</v>
       </c>
       <c r="E85" s="47" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F85" s="47" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G85" s="48" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="H85" s="26"/>
       <c r="I85" s="26"/>
@@ -28304,7 +28299,7 @@
     <row r="86" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="61"/>
       <c r="B86" s="39" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C86" s="49">
         <f t="shared" si="1"/>
@@ -28315,13 +28310,13 @@
         <v>Wed</v>
       </c>
       <c r="E86" s="26" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F86" s="26" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G86" s="50" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="H86" s="26"/>
       <c r="I86" s="26"/>
@@ -28335,7 +28330,7 @@
     <row r="87" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="61"/>
       <c r="B87" s="39" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C87" s="49">
         <f t="shared" si="1"/>
@@ -28346,13 +28341,13 @@
         <v>Thu</v>
       </c>
       <c r="E87" s="26" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F87" s="26" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G87" s="50" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="H87" s="26"/>
       <c r="I87" s="26"/>
@@ -28366,7 +28361,7 @@
     <row r="88" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="61"/>
       <c r="B88" s="39" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C88" s="49">
         <f t="shared" si="1"/>
@@ -28377,13 +28372,13 @@
         <v>Fri</v>
       </c>
       <c r="E88" s="26" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F88" s="26" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G88" s="50" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="H88" s="26"/>
       <c r="I88" s="26"/>
@@ -28397,7 +28392,7 @@
     <row r="89" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="61"/>
       <c r="B89" s="51" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C89" s="52">
         <f t="shared" si="1"/>
@@ -28408,13 +28403,13 @@
         <v>Mon</v>
       </c>
       <c r="E89" s="53" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F89" s="53" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G89" s="54" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H89" s="26"/>
       <c r="I89" s="26"/>
@@ -28428,7 +28423,7 @@
     <row r="90" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="62"/>
       <c r="B90" s="45" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C90" s="46">
         <f t="shared" si="1"/>
@@ -28439,13 +28434,13 @@
         <v>Tue</v>
       </c>
       <c r="E90" s="47" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F90" s="47" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G90" s="48" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H90" s="26"/>
       <c r="I90" s="26"/>
@@ -28459,7 +28454,7 @@
     <row r="91" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="39"/>
       <c r="B91" s="39" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C91" s="49">
         <f t="shared" si="1"/>
@@ -28470,13 +28465,13 @@
         <v>Wed</v>
       </c>
       <c r="E91" s="26" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F91" s="26" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G91" s="50" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="H91" s="26"/>
       <c r="I91" s="26"/>
@@ -28490,7 +28485,7 @@
     <row r="92" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="39"/>
       <c r="B92" s="39" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C92" s="49">
         <f t="shared" si="1"/>
@@ -28501,13 +28496,13 @@
         <v>Thu</v>
       </c>
       <c r="E92" s="26" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F92" s="26" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G92" s="50" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="H92" s="26"/>
       <c r="I92" s="26"/>
@@ -28521,7 +28516,7 @@
     <row r="93" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="39"/>
       <c r="B93" s="39" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C93" s="49">
         <f t="shared" si="1"/>
@@ -28532,13 +28527,13 @@
         <v>Fri</v>
       </c>
       <c r="E93" s="26" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F93" s="26" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G93" s="50" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="H93" s="26"/>
       <c r="I93" s="26"/>
@@ -28552,7 +28547,7 @@
     <row r="94" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="39"/>
       <c r="B94" s="51" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C94" s="52">
         <f t="shared" si="1"/>
@@ -28563,13 +28558,13 @@
         <v>Mon</v>
       </c>
       <c r="E94" s="55" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F94" s="55" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G94" s="54" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="H94" s="26"/>
       <c r="I94" s="26"/>
@@ -28583,7 +28578,7 @@
     <row r="95" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="39"/>
       <c r="B95" s="45" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C95" s="46">
         <f t="shared" si="1"/>
@@ -28594,13 +28589,13 @@
         <v>Tue</v>
       </c>
       <c r="E95" s="47" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F95" s="47" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G95" s="48" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H95" s="26"/>
       <c r="I95" s="26"/>
@@ -28614,7 +28609,7 @@
     <row r="96" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="39"/>
       <c r="B96" s="39" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C96" s="49">
         <f t="shared" si="1"/>
@@ -28625,13 +28620,13 @@
         <v>Wed</v>
       </c>
       <c r="E96" s="26" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F96" s="26" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G96" s="50" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H96" s="26"/>
       <c r="I96" s="26"/>
@@ -28645,7 +28640,7 @@
     <row r="97" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="39"/>
       <c r="B97" s="39" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C97" s="49">
         <f t="shared" si="1"/>
@@ -28656,13 +28651,13 @@
         <v>Thu</v>
       </c>
       <c r="E97" s="26" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F97" s="26" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G97" s="50" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="H97" s="26"/>
       <c r="I97" s="26"/>
@@ -28676,7 +28671,7 @@
     <row r="98" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="39"/>
       <c r="B98" s="39" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C98" s="49">
         <f t="shared" si="1"/>
@@ -28687,13 +28682,13 @@
         <v>Fri</v>
       </c>
       <c r="E98" s="26" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F98" s="26" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G98" s="50" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="H98" s="26"/>
       <c r="I98" s="26"/>
@@ -28707,7 +28702,7 @@
     <row r="99" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="39"/>
       <c r="B99" s="51" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C99" s="52">
         <f t="shared" si="1"/>
@@ -28718,13 +28713,13 @@
         <v>Mon</v>
       </c>
       <c r="E99" s="53" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F99" s="53" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G99" s="54" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="H99" s="26"/>
       <c r="I99" s="26"/>
@@ -28738,7 +28733,7 @@
     <row r="100" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="39"/>
       <c r="B100" s="45" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C100" s="46">
         <f t="shared" si="1"/>
@@ -28749,13 +28744,13 @@
         <v>Tue</v>
       </c>
       <c r="E100" s="47" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F100" s="47" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G100" s="48" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="H100" s="26"/>
       <c r="I100" s="26"/>
@@ -28769,7 +28764,7 @@
     <row r="101" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="39"/>
       <c r="B101" s="39" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C101" s="49">
         <f t="shared" si="1"/>
@@ -28780,13 +28775,13 @@
         <v>Wed</v>
       </c>
       <c r="E101" s="26" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F101" s="26" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G101" s="50" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H101" s="26"/>
       <c r="I101" s="26"/>
@@ -28800,7 +28795,7 @@
     <row r="102" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="39"/>
       <c r="B102" s="39" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C102" s="49">
         <f t="shared" si="1"/>
@@ -28811,13 +28806,13 @@
         <v>Thu</v>
       </c>
       <c r="E102" s="26" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F102" s="26" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G102" s="50" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H102" s="26"/>
       <c r="I102" s="26"/>
@@ -28831,7 +28826,7 @@
     <row r="103" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="39"/>
       <c r="B103" s="39" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C103" s="49">
         <f t="shared" si="1"/>
@@ -28842,13 +28837,13 @@
         <v>Fri</v>
       </c>
       <c r="E103" s="26" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F103" s="26" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G103" s="50" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="H103" s="26"/>
       <c r="I103" s="26"/>
@@ -28862,7 +28857,7 @@
     <row r="104" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="39"/>
       <c r="B104" s="51" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C104" s="52">
         <f t="shared" si="1"/>
@@ -28873,13 +28868,13 @@
         <v>Mon</v>
       </c>
       <c r="E104" s="55" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F104" s="55" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G104" s="54" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="H104" s="26"/>
       <c r="I104" s="26"/>
@@ -28893,7 +28888,7 @@
     <row r="105" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="39"/>
       <c r="B105" s="45" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C105" s="46">
         <f t="shared" si="1"/>
@@ -28904,10 +28899,10 @@
         <v>Tue</v>
       </c>
       <c r="E105" s="63" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F105" s="63" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="G105" s="64"/>
       <c r="H105" s="26"/>
@@ -28922,7 +28917,7 @@
     <row r="106" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="39"/>
       <c r="B106" s="39" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C106" s="49">
         <f t="shared" si="1"/>
@@ -28933,13 +28928,13 @@
         <v>Wed</v>
       </c>
       <c r="E106" s="26" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F106" s="26" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="G106" s="50" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H106" s="26"/>
       <c r="I106" s="26"/>
@@ -28953,7 +28948,7 @@
     <row r="107" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="39"/>
       <c r="B107" s="39" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C107" s="49">
         <f t="shared" si="1"/>
@@ -28964,13 +28959,13 @@
         <v>Thu</v>
       </c>
       <c r="E107" s="26" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F107" s="26" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="G107" s="50" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H107" s="26"/>
       <c r="I107" s="26"/>
@@ -28984,7 +28979,7 @@
     <row r="108" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="39"/>
       <c r="B108" s="39" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C108" s="49">
         <f t="shared" si="1"/>
@@ -28995,13 +28990,13 @@
         <v>Fri</v>
       </c>
       <c r="E108" s="26" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F108" s="26" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="G108" s="50" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="H108" s="26"/>
       <c r="I108" s="26"/>
@@ -29015,7 +29010,7 @@
     <row r="109" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="39"/>
       <c r="B109" s="39" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C109" s="49">
         <f t="shared" si="1"/>
@@ -29026,13 +29021,13 @@
         <v>Mon</v>
       </c>
       <c r="E109" s="26" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F109" s="26" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="G109" s="50" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="H109" s="26"/>
       <c r="I109" s="26"/>
@@ -29046,7 +29041,7 @@
     <row r="110" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="39"/>
       <c r="B110" s="45" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C110" s="46">
         <f t="shared" si="1"/>
@@ -29057,13 +29052,13 @@
         <v>Tue</v>
       </c>
       <c r="E110" s="65" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F110" s="65" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G110" s="66" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="H110" s="26"/>
       <c r="I110" s="26"/>
@@ -29077,7 +29072,7 @@
     <row r="111" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="39"/>
       <c r="B111" s="39" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C111" s="49">
         <f t="shared" si="1"/>
@@ -29088,13 +29083,13 @@
         <v>Wed</v>
       </c>
       <c r="E111" s="67" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F111" s="67" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G111" s="68" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="H111" s="26"/>
       <c r="I111" s="26"/>
@@ -29108,7 +29103,7 @@
     <row r="112" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="39"/>
       <c r="B112" s="39" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C112" s="49">
         <f t="shared" si="1"/>
@@ -29119,13 +29114,13 @@
         <v>Thu</v>
       </c>
       <c r="E112" s="67" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F112" s="67" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G112" s="68" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="H112" s="26"/>
       <c r="I112" s="26"/>
@@ -29139,7 +29134,7 @@
     <row r="113" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="39"/>
       <c r="B113" s="39" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C113" s="49">
         <f t="shared" si="1"/>
@@ -29150,13 +29145,13 @@
         <v>Fri</v>
       </c>
       <c r="E113" s="69" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="F113" s="69" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="G113" s="70" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="H113" s="26"/>
       <c r="I113" s="26"/>
@@ -29170,7 +29165,7 @@
     <row r="114" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="39"/>
       <c r="B114" s="51" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C114" s="52">
         <f t="shared" si="1"/>
@@ -29181,13 +29176,13 @@
         <v>Mon</v>
       </c>
       <c r="E114" s="55" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F114" s="55" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="G114" s="71" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="H114" s="26"/>
       <c r="I114" s="26"/>
@@ -29201,7 +29196,7 @@
     <row r="115" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="39"/>
       <c r="B115" s="45" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C115" s="46">
         <f t="shared" si="1"/>
@@ -29212,13 +29207,13 @@
         <v>Tue</v>
       </c>
       <c r="E115" s="72" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F115" s="72" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G115" s="73" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="H115" s="26"/>
       <c r="I115" s="26"/>
@@ -29232,7 +29227,7 @@
     <row r="116" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="39"/>
       <c r="B116" s="39" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C116" s="49">
         <f t="shared" si="1"/>
@@ -29243,13 +29238,13 @@
         <v>Wed</v>
       </c>
       <c r="E116" s="69" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F116" s="69" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G116" s="70" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H116" s="26"/>
       <c r="I116" s="26"/>
@@ -29263,7 +29258,7 @@
     <row r="117" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="39"/>
       <c r="B117" s="39" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C117" s="49">
         <f t="shared" si="1"/>
@@ -29274,13 +29269,13 @@
         <v>Thu</v>
       </c>
       <c r="E117" s="69" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F117" s="69" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G117" s="70" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H117" s="26"/>
       <c r="I117" s="26"/>
@@ -29294,7 +29289,7 @@
     <row r="118" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="39"/>
       <c r="B118" s="39" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C118" s="49">
         <f t="shared" si="1"/>
@@ -29305,13 +29300,13 @@
         <v>Fri</v>
       </c>
       <c r="E118" s="69" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F118" s="69" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G118" s="70" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H118" s="26"/>
       <c r="I118" s="26"/>
@@ -29325,7 +29320,7 @@
     <row r="119" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="39"/>
       <c r="B119" s="51" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C119" s="52">
         <f t="shared" si="1"/>
@@ -29336,13 +29331,13 @@
         <v>Mon</v>
       </c>
       <c r="E119" s="74" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F119" s="74" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="G119" s="75" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="H119" s="26"/>
       <c r="I119" s="26"/>
@@ -29356,7 +29351,7 @@
     <row r="120" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="39"/>
       <c r="B120" s="45" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C120" s="46">
         <f t="shared" si="1"/>
@@ -29367,13 +29362,13 @@
         <v>Tue</v>
       </c>
       <c r="E120" s="76" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F120" s="76" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G120" s="77" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H120" s="26"/>
       <c r="I120" s="26"/>
@@ -29387,7 +29382,7 @@
     <row r="121" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="39"/>
       <c r="B121" s="39" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C121" s="49">
         <f t="shared" si="1"/>
@@ -29398,13 +29393,13 @@
         <v>Wed</v>
       </c>
       <c r="E121" s="78" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F121" s="78" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G121" s="79" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H121" s="26"/>
       <c r="I121" s="26"/>
@@ -29418,7 +29413,7 @@
     <row r="122" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="39"/>
       <c r="B122" s="39" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C122" s="49">
         <f t="shared" si="1"/>
@@ -29429,13 +29424,13 @@
         <v>Thu</v>
       </c>
       <c r="E122" s="26" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F122" s="26" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G122" s="50" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="H122" s="26"/>
       <c r="I122" s="26"/>
@@ -29449,7 +29444,7 @@
     <row r="123" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="39"/>
       <c r="B123" s="39" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C123" s="49">
         <f t="shared" si="1"/>
@@ -29460,13 +29455,13 @@
         <v>Fri</v>
       </c>
       <c r="E123" s="26" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="F123" s="26" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G123" s="50" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="H123" s="26"/>
       <c r="I123" s="26"/>
@@ -29480,7 +29475,7 @@
     <row r="124" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="39"/>
       <c r="B124" s="51" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C124" s="52">
         <f t="shared" si="1"/>
@@ -29491,13 +29486,13 @@
         <v>Mon</v>
       </c>
       <c r="E124" s="53" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F124" s="53" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G124" s="54" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="H124" s="26"/>
       <c r="I124" s="26"/>
@@ -29511,7 +29506,7 @@
     <row r="125" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="39"/>
       <c r="B125" s="45" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C125" s="46">
         <f t="shared" si="1"/>
@@ -29522,13 +29517,13 @@
         <v>Tue</v>
       </c>
       <c r="E125" s="47" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="F125" s="47" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G125" s="48" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="H125" s="26"/>
       <c r="I125" s="26"/>
@@ -29542,7 +29537,7 @@
     <row r="126" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="39"/>
       <c r="B126" s="39" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C126" s="49">
         <f t="shared" si="1"/>
@@ -29553,13 +29548,13 @@
         <v>Wed</v>
       </c>
       <c r="E126" s="69" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F126" s="69" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G126" s="70" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H126" s="26"/>
       <c r="I126" s="26"/>
@@ -29573,7 +29568,7 @@
     <row r="127" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="39"/>
       <c r="B127" s="39" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C127" s="49">
         <f t="shared" si="1"/>
@@ -29584,13 +29579,13 @@
         <v>Thu</v>
       </c>
       <c r="E127" s="69" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F127" s="69" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G127" s="70" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H127" s="26"/>
       <c r="I127" s="26"/>
@@ -29604,7 +29599,7 @@
     <row r="128" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="39"/>
       <c r="B128" s="39" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C128" s="49">
         <f t="shared" si="1"/>
@@ -29615,13 +29610,13 @@
         <v>Fri</v>
       </c>
       <c r="E128" s="78" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F128" s="78" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="G128" s="79" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H128" s="26"/>
       <c r="I128" s="26"/>
@@ -29635,7 +29630,7 @@
     <row r="129" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="39"/>
       <c r="B129" s="51" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C129" s="52">
         <f t="shared" si="1"/>
@@ -29646,13 +29641,13 @@
         <v>Mon</v>
       </c>
       <c r="E129" s="80" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F129" s="80" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="G129" s="81" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H129" s="26"/>
       <c r="I129" s="26"/>
@@ -29666,7 +29661,7 @@
     <row r="130" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="39"/>
       <c r="B130" s="45" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C130" s="46">
         <f t="shared" si="1"/>
@@ -29677,13 +29672,13 @@
         <v>Tue</v>
       </c>
       <c r="E130" s="65" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="F130" s="65" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G130" s="66" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="H130" s="26"/>
       <c r="I130" s="26"/>
@@ -29697,7 +29692,7 @@
     <row r="131" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="39"/>
       <c r="B131" s="39" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C131" s="49">
         <f t="shared" si="1"/>
@@ -29708,13 +29703,13 @@
         <v>Wed</v>
       </c>
       <c r="E131" s="67" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F131" s="67" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G131" s="68" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="H131" s="26"/>
       <c r="I131" s="26"/>
@@ -29728,7 +29723,7 @@
     <row r="132" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="39"/>
       <c r="B132" s="39" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C132" s="49">
         <f t="shared" si="1"/>
@@ -29739,13 +29734,13 @@
         <v>Thu</v>
       </c>
       <c r="E132" s="69" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F132" s="69" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G132" s="70" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="H132" s="26"/>
       <c r="I132" s="26"/>
@@ -29759,7 +29754,7 @@
     <row r="133" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="39"/>
       <c r="B133" s="39" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C133" s="49">
         <f t="shared" si="1"/>
@@ -29770,13 +29765,13 @@
         <v>Fri</v>
       </c>
       <c r="E133" s="69" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F133" s="69" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G133" s="70" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="H133" s="26"/>
       <c r="I133" s="26"/>
@@ -29790,7 +29785,7 @@
     <row r="134" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="39"/>
       <c r="B134" s="51" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C134" s="52">
         <f t="shared" si="1"/>
@@ -29801,13 +29796,13 @@
         <v>Mon</v>
       </c>
       <c r="E134" s="82" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F134" s="82" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G134" s="83" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="H134" s="26"/>
       <c r="I134" s="26"/>
@@ -29821,7 +29816,7 @@
     <row r="135" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="51"/>
       <c r="B135" s="56" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C135" s="57">
         <f t="shared" si="1"/>
@@ -29832,13 +29827,13 @@
         <v>Tue</v>
       </c>
       <c r="E135" s="84" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F135" s="84" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G135" s="85" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="H135" s="26"/>
       <c r="I135" s="26"/>
@@ -29868,13 +29863,13 @@
     </row>
     <row r="137" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="86" t="s">
+        <v>344</v>
+      </c>
+      <c r="B137" s="26" t="s">
+        <v>345</v>
+      </c>
+      <c r="C137" s="26" t="s">
         <v>346</v>
-      </c>
-      <c r="B137" s="26" t="s">
-        <v>347</v>
-      </c>
-      <c r="C137" s="26" t="s">
-        <v>348</v>
       </c>
       <c r="D137" s="26"/>
       <c r="E137" s="26"/>
@@ -29892,10 +29887,10 @@
     <row r="138" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="26"/>
       <c r="B138" s="26" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C138" s="26" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D138" s="26"/>
       <c r="E138" s="26"/>
@@ -29913,10 +29908,10 @@
     <row r="139" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="26"/>
       <c r="B139" s="87" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C139" s="26" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D139" s="26"/>
       <c r="E139" s="26"/>
@@ -29934,10 +29929,10 @@
     <row r="140" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="26"/>
       <c r="B140" s="88" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C140" s="26" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D140" s="26"/>
       <c r="E140" s="26"/>
@@ -29955,10 +29950,10 @@
     <row r="141" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="26"/>
       <c r="B141" s="26" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C141" s="26" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D141" s="26"/>
       <c r="E141" s="26"/>
@@ -29976,10 +29971,10 @@
     <row r="142" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="26"/>
       <c r="B142" s="26" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C142" s="26" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D142" s="26"/>
       <c r="E142" s="26"/>
@@ -29997,10 +29992,10 @@
     <row r="143" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="26"/>
       <c r="B143" s="26" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C143" s="26" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D143" s="26"/>
       <c r="E143" s="26"/>
@@ -30018,10 +30013,10 @@
     <row r="144" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="26"/>
       <c r="B144" s="69" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C144" s="26" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D144" s="26"/>
       <c r="E144" s="26"/>
@@ -30039,10 +30034,10 @@
     <row r="145" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="26"/>
       <c r="B145" s="26" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C145" s="26" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D145" s="26"/>
       <c r="E145" s="26"/>
@@ -30060,10 +30055,10 @@
     <row r="146" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="26"/>
       <c r="B146" s="67" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C146" s="26" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D146" s="26"/>
       <c r="E146" s="26"/>
@@ -30081,10 +30076,10 @@
     <row r="147" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="26"/>
       <c r="B147" s="26" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C147" s="26" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D147" s="26"/>
       <c r="E147" s="26"/>
@@ -30102,10 +30097,10 @@
     <row r="148" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="26"/>
       <c r="B148" s="78" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C148" s="26" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D148" s="26"/>
       <c r="E148" s="26"/>
@@ -34218,7 +34213,7 @@
       <c r="C2" s="26"/>
       <c r="D2" s="26"/>
       <c r="E2" s="89" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="F2" s="28"/>
       <c r="G2" s="28"/>
@@ -34232,13 +34227,13 @@
     </row>
     <row r="3" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B3" s="26"/>
       <c r="C3" s="26"/>
       <c r="D3" s="26"/>
       <c r="E3" s="90" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F3" s="26"/>
       <c r="G3" s="26"/>
@@ -34252,7 +34247,7 @@
     </row>
     <row r="4" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="30" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B4" s="26"/>
       <c r="C4" s="26"/>
@@ -34284,24 +34279,24 @@
     </row>
     <row r="6" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B6" s="111" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C6" s="112"/>
       <c r="D6" s="32" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F6" s="32"/>
       <c r="G6" s="34" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="H6" s="35" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="I6" s="32"/>
       <c r="K6" s="34"/>
@@ -34311,24 +34306,24 @@
     </row>
     <row r="7" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B7" s="111" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C7" s="112"/>
       <c r="D7" s="32" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="F7" s="32"/>
       <c r="G7" s="34" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H7" s="35" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="K7" s="34"/>
       <c r="L7" s="34"/>
@@ -34337,17 +34332,17 @@
     </row>
     <row r="8" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="32" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B8" s="111" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C8" s="112"/>
       <c r="D8" s="32" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E8" s="36" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F8" s="36"/>
       <c r="G8" s="35"/>
@@ -34375,10 +34370,10 @@
     </row>
     <row r="10" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="40" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B10" s="41" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C10" s="41" t="s">
         <v>18</v>
@@ -34387,10 +34382,10 @@
         <v>19</v>
       </c>
       <c r="E10" s="42" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="F10" s="43" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="G10" s="26"/>
       <c r="H10" s="26"/>
@@ -34403,7 +34398,7 @@
     </row>
     <row r="11" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="44" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B11" s="45" t="s">
         <v>22</v>
@@ -34416,10 +34411,10 @@
         <v>Fri</v>
       </c>
       <c r="E11" s="47" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F11" s="48" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G11" s="26"/>
       <c r="H11" s="26"/>
@@ -34444,10 +34439,10 @@
         <v>Mon</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F12" s="50" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G12" s="26"/>
       <c r="H12" s="26"/>
@@ -34472,10 +34467,10 @@
         <v>Wed</v>
       </c>
       <c r="E13" s="53" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F13" s="54" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G13" s="26"/>
       <c r="H13" s="26"/>
@@ -34500,10 +34495,10 @@
         <v>Fri</v>
       </c>
       <c r="E14" s="47" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F14" s="48" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G14" s="26"/>
       <c r="H14" s="26"/>
@@ -34528,10 +34523,10 @@
         <v>Mon</v>
       </c>
       <c r="E15" s="26" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F15" s="50" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G15" s="26"/>
       <c r="H15" s="26"/>
@@ -34556,10 +34551,10 @@
         <v>Wed</v>
       </c>
       <c r="E16" s="53" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F16" s="54" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G16" s="26"/>
       <c r="H16" s="26"/>
@@ -34573,7 +34568,7 @@
     <row r="17" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="39"/>
       <c r="B17" s="45" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C17" s="46">
         <f t="shared" si="1"/>
@@ -34584,10 +34579,10 @@
         <v>Fri</v>
       </c>
       <c r="E17" s="47" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F17" s="48" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G17" s="26"/>
       <c r="H17" s="26"/>
@@ -34601,7 +34596,7 @@
     <row r="18" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="39"/>
       <c r="B18" s="39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C18" s="49">
         <f t="shared" si="1"/>
@@ -34612,10 +34607,10 @@
         <v>Mon</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F18" s="50" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G18" s="26"/>
       <c r="H18" s="26"/>
@@ -34629,7 +34624,7 @@
     <row r="19" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="39"/>
       <c r="B19" s="51" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19" s="52">
         <f t="shared" si="1"/>
@@ -34640,10 +34635,10 @@
         <v>Wed</v>
       </c>
       <c r="E19" s="53" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F19" s="54" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G19" s="26"/>
       <c r="H19" s="26"/>
@@ -34657,7 +34652,7 @@
     <row r="20" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="39"/>
       <c r="B20" s="45" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C20" s="46">
         <f t="shared" si="1"/>
@@ -34668,10 +34663,10 @@
         <v>Fri</v>
       </c>
       <c r="E20" s="72" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F20" s="73" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G20" s="26"/>
       <c r="H20" s="26"/>
@@ -34685,7 +34680,7 @@
     <row r="21" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="39"/>
       <c r="B21" s="39" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C21" s="49">
         <f t="shared" si="1"/>
@@ -34696,10 +34691,10 @@
         <v>Mon</v>
       </c>
       <c r="E21" s="26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F21" s="50" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G21" s="26"/>
       <c r="H21" s="26"/>
@@ -34713,7 +34708,7 @@
     <row r="22" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="39"/>
       <c r="B22" s="51" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C22" s="52">
         <f t="shared" si="1"/>
@@ -34724,10 +34719,10 @@
         <v>Wed</v>
       </c>
       <c r="E22" s="53" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F22" s="54" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G22" s="26"/>
       <c r="H22" s="26"/>
@@ -34741,7 +34736,7 @@
     <row r="23" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="39"/>
       <c r="B23" s="45" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C23" s="46">
         <f t="shared" si="1"/>
@@ -34752,10 +34747,10 @@
         <v>Fri</v>
       </c>
       <c r="E23" s="47" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F23" s="48" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G23" s="26"/>
       <c r="H23" s="26"/>
@@ -34769,7 +34764,7 @@
     <row r="24" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="39"/>
       <c r="B24" s="39" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C24" s="49">
         <f t="shared" si="1"/>
@@ -34780,10 +34775,10 @@
         <v>Mon</v>
       </c>
       <c r="E24" s="26" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F24" s="50" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G24" s="26"/>
       <c r="H24" s="26"/>
@@ -34797,7 +34792,7 @@
     <row r="25" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="39"/>
       <c r="B25" s="51" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C25" s="52">
         <f t="shared" si="1"/>
@@ -34808,10 +34803,10 @@
         <v>Wed</v>
       </c>
       <c r="E25" s="53" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F25" s="54" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G25" s="26"/>
       <c r="H25" s="26"/>
@@ -34825,7 +34820,7 @@
     <row r="26" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="39"/>
       <c r="B26" s="45" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C26" s="46">
         <f t="shared" si="1"/>
@@ -34836,10 +34831,10 @@
         <v>Fri</v>
       </c>
       <c r="E26" s="47" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F26" s="48" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G26" s="26"/>
       <c r="H26" s="26"/>
@@ -34853,7 +34848,7 @@
     <row r="27" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="39"/>
       <c r="B27" s="39" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C27" s="49">
         <f t="shared" si="1"/>
@@ -34864,10 +34859,10 @@
         <v>Mon</v>
       </c>
       <c r="E27" s="26" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F27" s="50" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G27" s="26"/>
       <c r="H27" s="26"/>
@@ -34881,7 +34876,7 @@
     <row r="28" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="39"/>
       <c r="B28" s="51" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C28" s="52">
         <f t="shared" si="1"/>
@@ -34892,10 +34887,10 @@
         <v>Wed</v>
       </c>
       <c r="E28" s="53" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F28" s="54" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G28" s="26"/>
       <c r="H28" s="26"/>
@@ -34909,7 +34904,7 @@
     <row r="29" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="39"/>
       <c r="B29" s="45" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C29" s="46">
         <f t="shared" si="1"/>
@@ -34920,10 +34915,10 @@
         <v>Fri</v>
       </c>
       <c r="E29" s="47" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F29" s="48" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G29" s="26"/>
       <c r="H29" s="26"/>
@@ -34937,7 +34932,7 @@
     <row r="30" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="39"/>
       <c r="B30" s="39" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C30" s="49">
         <f t="shared" si="1"/>
@@ -34948,10 +34943,10 @@
         <v>Mon</v>
       </c>
       <c r="E30" s="69" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F30" s="70" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G30" s="26"/>
       <c r="H30" s="26"/>
@@ -34965,7 +34960,7 @@
     <row r="31" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="39"/>
       <c r="B31" s="51" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C31" s="52">
         <f t="shared" si="1"/>
@@ -34976,10 +34971,10 @@
         <v>Wed</v>
       </c>
       <c r="E31" s="53" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F31" s="54" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G31" s="26"/>
       <c r="H31" s="26"/>
@@ -34993,7 +34988,7 @@
     <row r="32" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="39"/>
       <c r="B32" s="45" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C32" s="46">
         <f t="shared" si="1"/>
@@ -35004,10 +34999,10 @@
         <v>Fri</v>
       </c>
       <c r="E32" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F32" s="48" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G32" s="26"/>
       <c r="H32" s="26"/>
@@ -35021,7 +35016,7 @@
     <row r="33" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="39"/>
       <c r="B33" s="39" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C33" s="49">
         <f t="shared" si="1"/>
@@ -35032,10 +35027,10 @@
         <v>Mon</v>
       </c>
       <c r="E33" s="26" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F33" s="50" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G33" s="26"/>
       <c r="H33" s="26"/>
@@ -35049,7 +35044,7 @@
     <row r="34" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="39"/>
       <c r="B34" s="51" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C34" s="52">
         <f t="shared" si="1"/>
@@ -35060,10 +35055,10 @@
         <v>Wed</v>
       </c>
       <c r="E34" s="53" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F34" s="54" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G34" s="26"/>
       <c r="H34" s="26"/>
@@ -35077,7 +35072,7 @@
     <row r="35" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="39"/>
       <c r="B35" s="45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C35" s="46">
         <f t="shared" si="1"/>
@@ -35088,10 +35083,10 @@
         <v>Fri</v>
       </c>
       <c r="E35" s="47" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F35" s="48" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G35" s="26"/>
       <c r="H35" s="26"/>
@@ -35105,7 +35100,7 @@
     <row r="36" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="39"/>
       <c r="B36" s="39" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C36" s="49">
         <f t="shared" si="1"/>
@@ -35116,10 +35111,10 @@
         <v>Mon</v>
       </c>
       <c r="E36" s="26" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F36" s="50" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G36" s="26"/>
       <c r="H36" s="26"/>
@@ -35133,7 +35128,7 @@
     <row r="37" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="39"/>
       <c r="B37" s="51" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C37" s="52">
         <f t="shared" si="1"/>
@@ -35144,10 +35139,10 @@
         <v>Wed</v>
       </c>
       <c r="E37" s="53" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F37" s="54" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G37" s="26"/>
       <c r="H37" s="26"/>
@@ -35161,7 +35156,7 @@
     <row r="38" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="39"/>
       <c r="B38" s="45" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C38" s="46">
         <f t="shared" si="1"/>
@@ -35172,10 +35167,10 @@
         <v>Fri</v>
       </c>
       <c r="E38" s="47" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F38" s="48" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G38" s="26"/>
       <c r="H38" s="26"/>
@@ -35189,7 +35184,7 @@
     <row r="39" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="39"/>
       <c r="B39" s="39" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C39" s="49">
         <f t="shared" si="1"/>
@@ -35200,10 +35195,10 @@
         <v>Mon</v>
       </c>
       <c r="E39" s="26" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F39" s="50" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G39" s="26"/>
       <c r="H39" s="26"/>
@@ -35217,7 +35212,7 @@
     <row r="40" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="39"/>
       <c r="B40" s="51" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C40" s="52">
         <f t="shared" si="1"/>
@@ -35228,10 +35223,10 @@
         <v>Wed</v>
       </c>
       <c r="E40" s="55" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F40" s="71" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G40" s="26"/>
       <c r="H40" s="26"/>
@@ -35245,7 +35240,7 @@
     <row r="41" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="39"/>
       <c r="B41" s="45" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C41" s="46">
         <f t="shared" si="1"/>
@@ -35256,10 +35251,10 @@
         <v>Fri</v>
       </c>
       <c r="E41" s="47" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F41" s="48" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G41" s="26"/>
       <c r="H41" s="26"/>
@@ -35273,7 +35268,7 @@
     <row r="42" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="39"/>
       <c r="B42" s="39" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C42" s="49">
         <f t="shared" si="1"/>
@@ -35284,10 +35279,10 @@
         <v>Mon</v>
       </c>
       <c r="E42" s="26" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F42" s="50" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G42" s="26"/>
       <c r="H42" s="26"/>
@@ -35301,7 +35296,7 @@
     <row r="43" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="39"/>
       <c r="B43" s="51" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C43" s="52">
         <f t="shared" si="1"/>
@@ -35312,10 +35307,10 @@
         <v>Wed</v>
       </c>
       <c r="E43" s="53" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F43" s="54" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G43" s="26"/>
       <c r="H43" s="26"/>
@@ -35329,7 +35324,7 @@
     <row r="44" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="39"/>
       <c r="B44" s="45" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C44" s="46">
         <f t="shared" si="1"/>
@@ -35340,10 +35335,10 @@
         <v>Fri</v>
       </c>
       <c r="E44" s="47" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F44" s="48" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G44" s="26"/>
       <c r="H44" s="26"/>
@@ -35357,7 +35352,7 @@
     <row r="45" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="39"/>
       <c r="B45" s="39" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C45" s="49">
         <f t="shared" si="1"/>
@@ -35368,10 +35363,10 @@
         <v>Mon</v>
       </c>
       <c r="E45" s="26" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F45" s="50" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G45" s="26"/>
       <c r="H45" s="26"/>
@@ -35385,7 +35380,7 @@
     <row r="46" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="39"/>
       <c r="B46" s="51" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C46" s="52">
         <f t="shared" si="1"/>
@@ -35396,10 +35391,10 @@
         <v>Wed</v>
       </c>
       <c r="E46" s="53" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F46" s="54" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G46" s="26"/>
       <c r="H46" s="26"/>
@@ -35413,7 +35408,7 @@
     <row r="47" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="39"/>
       <c r="B47" s="45" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C47" s="46">
         <f t="shared" si="1"/>
@@ -35424,10 +35419,10 @@
         <v>Fri</v>
       </c>
       <c r="E47" s="47" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F47" s="48" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G47" s="26"/>
       <c r="H47" s="26"/>
@@ -35441,7 +35436,7 @@
     <row r="48" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="39"/>
       <c r="B48" s="39" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C48" s="49">
         <f t="shared" si="1"/>
@@ -35452,10 +35447,10 @@
         <v>Mon</v>
       </c>
       <c r="E48" s="26" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F48" s="50" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G48" s="26"/>
       <c r="H48" s="26"/>
@@ -35469,7 +35464,7 @@
     <row r="49" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="39"/>
       <c r="B49" s="51" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C49" s="52">
         <f t="shared" si="1"/>
@@ -35480,10 +35475,10 @@
         <v>Wed</v>
       </c>
       <c r="E49" s="53" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F49" s="54" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G49" s="26"/>
       <c r="H49" s="26"/>
@@ -35497,7 +35492,7 @@
     <row r="50" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="39"/>
       <c r="B50" s="45" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C50" s="46">
         <f t="shared" si="1"/>
@@ -35508,10 +35503,10 @@
         <v>Fri</v>
       </c>
       <c r="E50" s="72" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F50" s="73" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G50" s="26"/>
       <c r="H50" s="26"/>
@@ -35525,7 +35520,7 @@
     <row r="51" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="39"/>
       <c r="B51" s="39" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C51" s="49">
         <f t="shared" si="1"/>
@@ -35536,10 +35531,10 @@
         <v>Mon</v>
       </c>
       <c r="E51" s="26" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F51" s="50" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G51" s="26"/>
       <c r="H51" s="26"/>
@@ -35553,7 +35548,7 @@
     <row r="52" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="39"/>
       <c r="B52" s="51" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C52" s="52">
         <f t="shared" si="1"/>
@@ -35564,10 +35559,10 @@
         <v>Wed</v>
       </c>
       <c r="E52" s="53" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F52" s="54" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G52" s="26"/>
       <c r="H52" s="26"/>
@@ -35581,7 +35576,7 @@
     <row r="53" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="39"/>
       <c r="B53" s="45" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C53" s="46">
         <f t="shared" si="1"/>
@@ -35592,10 +35587,10 @@
         <v>Fri</v>
       </c>
       <c r="E53" s="47" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F53" s="48" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G53" s="26"/>
       <c r="H53" s="26"/>
@@ -35609,7 +35604,7 @@
     <row r="54" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="39"/>
       <c r="B54" s="39" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C54" s="49">
         <f t="shared" si="1"/>
@@ -35620,10 +35615,10 @@
         <v>Mon</v>
       </c>
       <c r="E54" s="26" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F54" s="50" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G54" s="26"/>
       <c r="H54" s="26"/>
@@ -35637,7 +35632,7 @@
     <row r="55" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="39"/>
       <c r="B55" s="51" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C55" s="52">
         <f t="shared" si="1"/>
@@ -35648,10 +35643,10 @@
         <v>Wed</v>
       </c>
       <c r="E55" s="53" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F55" s="54" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G55" s="26"/>
       <c r="H55" s="26"/>
@@ -35665,7 +35660,7 @@
     <row r="56" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="39"/>
       <c r="B56" s="45" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C56" s="46">
         <f t="shared" si="1"/>
@@ -35676,10 +35671,10 @@
         <v>Fri</v>
       </c>
       <c r="E56" s="47" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F56" s="48" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G56" s="26"/>
       <c r="H56" s="26"/>
@@ -35693,7 +35688,7 @@
     <row r="57" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="39"/>
       <c r="B57" s="39" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C57" s="49">
         <f t="shared" si="1"/>
@@ -35704,10 +35699,10 @@
         <v>Mon</v>
       </c>
       <c r="E57" s="26" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F57" s="50" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G57" s="26"/>
       <c r="H57" s="26"/>
@@ -35721,7 +35716,7 @@
     <row r="58" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="39"/>
       <c r="B58" s="51" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C58" s="52">
         <f t="shared" si="1"/>
@@ -35732,10 +35727,10 @@
         <v>Wed</v>
       </c>
       <c r="E58" s="53" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F58" s="54" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G58" s="26"/>
       <c r="H58" s="26"/>
@@ -35749,7 +35744,7 @@
     <row r="59" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="39"/>
       <c r="B59" s="45" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C59" s="46">
         <f t="shared" si="1"/>
@@ -35760,10 +35755,10 @@
         <v>Fri</v>
       </c>
       <c r="E59" s="47" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F59" s="48" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G59" s="26"/>
       <c r="H59" s="26"/>
@@ -35777,7 +35772,7 @@
     <row r="60" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="39"/>
       <c r="B60" s="39" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C60" s="49">
         <f t="shared" si="1"/>
@@ -35788,10 +35783,10 @@
         <v>Mon</v>
       </c>
       <c r="E60" s="69" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F60" s="70" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G60" s="26"/>
       <c r="H60" s="26"/>
@@ -35805,7 +35800,7 @@
     <row r="61" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="39"/>
       <c r="B61" s="51" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C61" s="52">
         <f t="shared" si="1"/>
@@ -35816,10 +35811,10 @@
         <v>Wed</v>
       </c>
       <c r="E61" s="91" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F61" s="92" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G61" s="26"/>
       <c r="H61" s="26"/>
@@ -35832,10 +35827,10 @@
     </row>
     <row r="62" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="44" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B62" s="45" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C62" s="46">
         <f t="shared" si="1"/>
@@ -35846,10 +35841,10 @@
         <v>Fri</v>
       </c>
       <c r="E62" s="47" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F62" s="48" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G62" s="26"/>
       <c r="H62" s="26"/>
@@ -35863,7 +35858,7 @@
     <row r="63" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="61"/>
       <c r="B63" s="39" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C63" s="49">
         <f t="shared" si="1"/>
@@ -35874,10 +35869,10 @@
         <v>Mon</v>
       </c>
       <c r="E63" s="26" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F63" s="50" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G63" s="26"/>
       <c r="H63" s="26"/>
@@ -35891,7 +35886,7 @@
     <row r="64" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="61"/>
       <c r="B64" s="51" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C64" s="52">
         <f t="shared" si="1"/>
@@ -35902,10 +35897,10 @@
         <v>Wed</v>
       </c>
       <c r="E64" s="53" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F64" s="54" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G64" s="26"/>
       <c r="H64" s="26"/>
@@ -35919,7 +35914,7 @@
     <row r="65" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="61"/>
       <c r="B65" s="45" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C65" s="46">
         <f t="shared" si="1"/>
@@ -35930,10 +35925,10 @@
         <v>Fri</v>
       </c>
       <c r="E65" s="47" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F65" s="48" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G65" s="26"/>
       <c r="H65" s="26"/>
@@ -35947,7 +35942,7 @@
     <row r="66" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="61"/>
       <c r="B66" s="39" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C66" s="49">
         <f t="shared" si="1"/>
@@ -35958,10 +35953,10 @@
         <v>Mon</v>
       </c>
       <c r="E66" s="26" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F66" s="50" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G66" s="26"/>
       <c r="H66" s="26"/>
@@ -35975,7 +35970,7 @@
     <row r="67" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="62"/>
       <c r="B67" s="51" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C67" s="52">
         <f t="shared" si="1"/>
@@ -35986,10 +35981,10 @@
         <v>Wed</v>
       </c>
       <c r="E67" s="53" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F67" s="54" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G67" s="26"/>
       <c r="H67" s="26"/>
@@ -36003,7 +35998,7 @@
     <row r="68" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="39"/>
       <c r="B68" s="45" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C68" s="46">
         <f t="shared" si="1"/>
@@ -36014,10 +36009,10 @@
         <v>Fri</v>
       </c>
       <c r="E68" s="47" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F68" s="48" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G68" s="26"/>
       <c r="H68" s="26"/>
@@ -36031,7 +36026,7 @@
     <row r="69" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="39"/>
       <c r="B69" s="39" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C69" s="49">
         <f t="shared" si="1"/>
@@ -36042,10 +36037,10 @@
         <v>Mon</v>
       </c>
       <c r="E69" s="26" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F69" s="50" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G69" s="26"/>
       <c r="H69" s="26"/>
@@ -36059,7 +36054,7 @@
     <row r="70" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="39"/>
       <c r="B70" s="51" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C70" s="52">
         <f t="shared" si="1"/>
@@ -36070,10 +36065,10 @@
         <v>Wed</v>
       </c>
       <c r="E70" s="53" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F70" s="54" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G70" s="26"/>
       <c r="H70" s="26"/>
@@ -36087,7 +36082,7 @@
     <row r="71" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="39"/>
       <c r="B71" s="45" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C71" s="46">
         <f t="shared" si="1"/>
@@ -36098,10 +36093,10 @@
         <v>Fri</v>
       </c>
       <c r="E71" s="72" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F71" s="73" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="G71" s="26"/>
       <c r="H71" s="26"/>
@@ -36115,7 +36110,7 @@
     <row r="72" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="39"/>
       <c r="B72" s="39" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C72" s="49">
         <f t="shared" si="1"/>
@@ -36126,10 +36121,10 @@
         <v>Mon</v>
       </c>
       <c r="E72" s="26" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F72" s="50" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G72" s="26"/>
       <c r="H72" s="26"/>
@@ -36143,7 +36138,7 @@
     <row r="73" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="39"/>
       <c r="B73" s="51" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C73" s="52">
         <f t="shared" si="1"/>
@@ -36154,10 +36149,10 @@
         <v>Wed</v>
       </c>
       <c r="E73" s="53" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F73" s="54" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G73" s="26"/>
       <c r="H73" s="26"/>
@@ -36171,7 +36166,7 @@
     <row r="74" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="39"/>
       <c r="B74" s="45" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C74" s="46">
         <f t="shared" si="1"/>
@@ -36182,10 +36177,10 @@
         <v>Fri</v>
       </c>
       <c r="E74" s="47" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F74" s="48" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G74" s="26"/>
       <c r="H74" s="26"/>
@@ -36199,7 +36194,7 @@
     <row r="75" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="39"/>
       <c r="B75" s="39" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C75" s="49">
         <f t="shared" si="1"/>
@@ -36210,10 +36205,10 @@
         <v>Mon</v>
       </c>
       <c r="E75" s="26" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F75" s="50" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G75" s="26"/>
       <c r="H75" s="26"/>
@@ -36227,7 +36222,7 @@
     <row r="76" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="39"/>
       <c r="B76" s="51" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C76" s="52">
         <f t="shared" si="1"/>
@@ -36238,10 +36233,10 @@
         <v>Wed</v>
       </c>
       <c r="E76" s="53" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F76" s="54" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G76" s="26"/>
       <c r="H76" s="26"/>
@@ -36255,7 +36250,7 @@
     <row r="77" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="39"/>
       <c r="B77" s="45" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C77" s="46">
         <f t="shared" si="1"/>
@@ -36266,10 +36261,10 @@
         <v>Fri</v>
       </c>
       <c r="E77" s="47" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F77" s="48" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G77" s="26"/>
       <c r="H77" s="26"/>
@@ -36283,7 +36278,7 @@
     <row r="78" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="39"/>
       <c r="B78" s="39" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C78" s="49">
         <f t="shared" si="1"/>
@@ -36294,10 +36289,10 @@
         <v>Mon</v>
       </c>
       <c r="E78" s="26" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F78" s="50" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G78" s="26"/>
       <c r="H78" s="26"/>
@@ -36311,7 +36306,7 @@
     <row r="79" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="39"/>
       <c r="B79" s="51" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C79" s="52">
         <f t="shared" si="1"/>
@@ -36322,10 +36317,10 @@
         <v>Wed</v>
       </c>
       <c r="E79" s="53" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F79" s="54" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G79" s="26"/>
       <c r="H79" s="26"/>
@@ -36339,7 +36334,7 @@
     <row r="80" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="39"/>
       <c r="B80" s="45" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C80" s="46">
         <f t="shared" si="1"/>
@@ -36350,10 +36345,10 @@
         <v>Fri</v>
       </c>
       <c r="E80" s="47" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F80" s="48" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="G80" s="26"/>
       <c r="H80" s="26"/>
@@ -36367,7 +36362,7 @@
     <row r="81" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="39"/>
       <c r="B81" s="39" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C81" s="49">
         <f t="shared" si="1"/>
@@ -36378,10 +36373,10 @@
         <v>Mon</v>
       </c>
       <c r="E81" s="69" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F81" s="70" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G81" s="26"/>
       <c r="H81" s="26"/>
@@ -36395,7 +36390,7 @@
     <row r="82" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="39"/>
       <c r="B82" s="51" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C82" s="52">
         <f t="shared" si="1"/>
@@ -36406,10 +36401,10 @@
         <v>Wed</v>
       </c>
       <c r="E82" s="91" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F82" s="92" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G82" s="26"/>
       <c r="H82" s="26"/>
@@ -36422,10 +36417,10 @@
     </row>
     <row r="83" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="44" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B83" s="45" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C83" s="46">
         <f t="shared" si="1"/>
@@ -36436,10 +36431,10 @@
         <v>Fri</v>
       </c>
       <c r="E83" s="47" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F83" s="48" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G83" s="26"/>
       <c r="H83" s="26"/>
@@ -36453,7 +36448,7 @@
     <row r="84" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="61"/>
       <c r="B84" s="39" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C84" s="49">
         <f t="shared" si="1"/>
@@ -36464,10 +36459,10 @@
         <v>Mon</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F84" s="50" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G84" s="26"/>
       <c r="H84" s="26"/>
@@ -36481,7 +36476,7 @@
     <row r="85" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="61"/>
       <c r="B85" s="51" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C85" s="52">
         <f t="shared" si="1"/>
@@ -36492,10 +36487,10 @@
         <v>Wed</v>
       </c>
       <c r="E85" s="53" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F85" s="54" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G85" s="26"/>
       <c r="H85" s="26"/>
@@ -36509,7 +36504,7 @@
     <row r="86" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="61"/>
       <c r="B86" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C86" s="46">
         <f t="shared" si="1"/>
@@ -36520,10 +36515,10 @@
         <v>Fri</v>
       </c>
       <c r="E86" s="47" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F86" s="48" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G86" s="26"/>
       <c r="H86" s="26"/>
@@ -36537,7 +36532,7 @@
     <row r="87" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="61"/>
       <c r="B87" s="39" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C87" s="49">
         <f t="shared" si="1"/>
@@ -36548,10 +36543,10 @@
         <v>Mon</v>
       </c>
       <c r="E87" s="26" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F87" s="50" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G87" s="26"/>
       <c r="H87" s="26"/>
@@ -36565,7 +36560,7 @@
     <row r="88" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="62"/>
       <c r="B88" s="51" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C88" s="52">
         <f t="shared" si="1"/>
@@ -36576,10 +36571,10 @@
         <v>Wed</v>
       </c>
       <c r="E88" s="53" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F88" s="54" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G88" s="26"/>
       <c r="H88" s="26"/>
@@ -36593,7 +36588,7 @@
     <row r="89" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="39"/>
       <c r="B89" s="45" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C89" s="46">
         <f t="shared" si="1"/>
@@ -36604,10 +36599,10 @@
         <v>Fri</v>
       </c>
       <c r="E89" s="47" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F89" s="48" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G89" s="26"/>
       <c r="H89" s="26"/>
@@ -36621,7 +36616,7 @@
     <row r="90" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="39"/>
       <c r="B90" s="39" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C90" s="49">
         <f t="shared" si="1"/>
@@ -36632,10 +36627,10 @@
         <v>Mon</v>
       </c>
       <c r="E90" s="26" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F90" s="50" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G90" s="26"/>
       <c r="H90" s="26"/>
@@ -36649,7 +36644,7 @@
     <row r="91" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="39"/>
       <c r="B91" s="51" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C91" s="52">
         <f t="shared" si="1"/>
@@ -36660,10 +36655,10 @@
         <v>Wed</v>
       </c>
       <c r="E91" s="53" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F91" s="54" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G91" s="26"/>
       <c r="H91" s="26"/>
@@ -36677,7 +36672,7 @@
     <row r="92" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="39"/>
       <c r="B92" s="45" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C92" s="46">
         <f t="shared" si="1"/>
@@ -36688,10 +36683,10 @@
         <v>Fri</v>
       </c>
       <c r="E92" s="72" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F92" s="73" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G92" s="26"/>
       <c r="H92" s="26"/>
@@ -36705,7 +36700,7 @@
     <row r="93" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="39"/>
       <c r="B93" s="39" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C93" s="49">
         <f t="shared" si="1"/>
@@ -36716,10 +36711,10 @@
         <v>Mon</v>
       </c>
       <c r="E93" s="26" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F93" s="50" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G93" s="26"/>
       <c r="H93" s="26"/>
@@ -36733,7 +36728,7 @@
     <row r="94" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="39"/>
       <c r="B94" s="51" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C94" s="52">
         <f t="shared" si="1"/>
@@ -36744,10 +36739,10 @@
         <v>Wed</v>
       </c>
       <c r="E94" s="53" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F94" s="54" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G94" s="26"/>
       <c r="H94" s="26"/>
@@ -36761,7 +36756,7 @@
     <row r="95" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="39"/>
       <c r="B95" s="45" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C95" s="46">
         <f t="shared" si="1"/>
@@ -36772,10 +36767,10 @@
         <v>Fri</v>
       </c>
       <c r="E95" s="47" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F95" s="48" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G95" s="26"/>
       <c r="H95" s="26"/>
@@ -36789,7 +36784,7 @@
     <row r="96" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="39"/>
       <c r="B96" s="39" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C96" s="49">
         <f t="shared" si="1"/>
@@ -36800,10 +36795,10 @@
         <v>Mon</v>
       </c>
       <c r="E96" s="26" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F96" s="50" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G96" s="26"/>
       <c r="H96" s="26"/>
@@ -36817,7 +36812,7 @@
     <row r="97" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="39"/>
       <c r="B97" s="51" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C97" s="52">
         <f t="shared" si="1"/>
@@ -36828,10 +36823,10 @@
         <v>Wed</v>
       </c>
       <c r="E97" s="53" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F97" s="54" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G97" s="26"/>
       <c r="H97" s="26"/>
@@ -36845,7 +36840,7 @@
     <row r="98" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="39"/>
       <c r="B98" s="45" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C98" s="46">
         <f t="shared" si="1"/>
@@ -36856,10 +36851,10 @@
         <v>Fri</v>
       </c>
       <c r="E98" s="47" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F98" s="48" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G98" s="26"/>
       <c r="H98" s="26"/>
@@ -36873,7 +36868,7 @@
     <row r="99" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="39"/>
       <c r="B99" s="39" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C99" s="49">
         <f t="shared" si="1"/>
@@ -36884,10 +36879,10 @@
         <v>Mon</v>
       </c>
       <c r="E99" s="26" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F99" s="50" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G99" s="26"/>
       <c r="H99" s="26"/>
@@ -36901,7 +36896,7 @@
     <row r="100" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="39"/>
       <c r="B100" s="51" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C100" s="52">
         <f t="shared" si="1"/>
@@ -36912,10 +36907,10 @@
         <v>Wed</v>
       </c>
       <c r="E100" s="53" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F100" s="54" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G100" s="26"/>
       <c r="H100" s="26"/>
@@ -36929,7 +36924,7 @@
     <row r="101" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="39"/>
       <c r="B101" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C101" s="46">
         <f t="shared" si="1"/>
@@ -36940,10 +36935,10 @@
         <v>Fri</v>
       </c>
       <c r="E101" s="47" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F101" s="48" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G101" s="26"/>
       <c r="H101" s="26"/>
@@ -36957,7 +36952,7 @@
     <row r="102" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="39"/>
       <c r="B102" s="39" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C102" s="49">
         <f t="shared" si="1"/>
@@ -36968,10 +36963,10 @@
         <v>Mon</v>
       </c>
       <c r="E102" s="69" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F102" s="70" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G102" s="26"/>
       <c r="H102" s="26"/>
@@ -36985,7 +36980,7 @@
     <row r="103" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="39"/>
       <c r="B103" s="51" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C103" s="52">
         <f t="shared" si="1"/>
@@ -36996,10 +36991,10 @@
         <v>Wed</v>
       </c>
       <c r="E103" s="93" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F103" s="94" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="G103" s="26"/>
       <c r="H103" s="26"/>
@@ -37013,7 +37008,7 @@
     <row r="104" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="39"/>
       <c r="B104" s="45" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C104" s="46">
         <f t="shared" si="1"/>
@@ -37024,10 +37019,10 @@
         <v>Fri</v>
       </c>
       <c r="E104" s="47" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F104" s="48" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="G104" s="26"/>
       <c r="H104" s="26"/>
@@ -37041,7 +37036,7 @@
     <row r="105" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="39"/>
       <c r="B105" s="39" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C105" s="49">
         <f t="shared" si="1"/>
@@ -37052,10 +37047,10 @@
         <v>Mon</v>
       </c>
       <c r="E105" s="26" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F105" s="50" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="G105" s="26"/>
       <c r="H105" s="26"/>
@@ -37069,7 +37064,7 @@
     <row r="106" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="39"/>
       <c r="B106" s="51" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C106" s="52">
         <f t="shared" si="1"/>
@@ -37080,10 +37075,10 @@
         <v>Wed</v>
       </c>
       <c r="E106" s="53" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F106" s="54" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="G106" s="26"/>
       <c r="H106" s="26"/>
@@ -37097,7 +37092,7 @@
     <row r="107" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="39"/>
       <c r="B107" s="45" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C107" s="46">
         <f t="shared" si="1"/>
@@ -37108,10 +37103,10 @@
         <v>Fri</v>
       </c>
       <c r="E107" s="47" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F107" s="48" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="G107" s="26"/>
       <c r="H107" s="26"/>
@@ -37125,7 +37120,7 @@
     <row r="108" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="39"/>
       <c r="B108" s="39" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C108" s="49">
         <f t="shared" si="1"/>
@@ -37136,10 +37131,10 @@
         <v>Mon</v>
       </c>
       <c r="E108" s="67" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F108" s="68" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G108" s="26"/>
       <c r="H108" s="26"/>
@@ -37153,7 +37148,7 @@
     <row r="109" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="39"/>
       <c r="B109" s="51" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C109" s="52">
         <f t="shared" si="1"/>
@@ -37164,10 +37159,10 @@
         <v>Wed</v>
       </c>
       <c r="E109" s="74" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F109" s="75" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G109" s="26"/>
       <c r="H109" s="26"/>
@@ -37181,7 +37176,7 @@
     <row r="110" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="39"/>
       <c r="B110" s="45" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C110" s="46">
         <f t="shared" si="1"/>
@@ -37192,10 +37187,10 @@
         <v>Fri</v>
       </c>
       <c r="E110" s="63" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F110" s="95" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G110" s="26"/>
       <c r="H110" s="26"/>
@@ -37209,7 +37204,7 @@
     <row r="111" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="39"/>
       <c r="B111" s="39" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C111" s="49">
         <f t="shared" si="1"/>
@@ -37220,10 +37215,10 @@
         <v>Mon</v>
       </c>
       <c r="E111" s="69" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="F111" s="70" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G111" s="26"/>
       <c r="H111" s="26"/>
@@ -37237,7 +37232,7 @@
     <row r="112" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="39"/>
       <c r="B112" s="51" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C112" s="52">
         <f t="shared" si="1"/>
@@ -37248,10 +37243,10 @@
         <v>Wed</v>
       </c>
       <c r="E112" s="55" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F112" s="71" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="G112" s="26"/>
       <c r="H112" s="26"/>
@@ -37265,7 +37260,7 @@
     <row r="113" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="39"/>
       <c r="B113" s="45" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C113" s="46">
         <f t="shared" si="1"/>
@@ -37276,10 +37271,10 @@
         <v>Fri</v>
       </c>
       <c r="E113" s="72" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F113" s="73" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G113" s="26"/>
       <c r="H113" s="26"/>
@@ -37293,7 +37288,7 @@
     <row r="114" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="39"/>
       <c r="B114" s="39" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C114" s="49">
         <f t="shared" si="1"/>
@@ -37304,10 +37299,10 @@
         <v>Mon</v>
       </c>
       <c r="E114" s="69" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F114" s="70" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G114" s="26"/>
       <c r="H114" s="26"/>
@@ -37321,7 +37316,7 @@
     <row r="115" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="39"/>
       <c r="B115" s="51" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C115" s="52">
         <f t="shared" si="1"/>
@@ -37332,10 +37327,10 @@
         <v>Wed</v>
       </c>
       <c r="E115" s="55" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F115" s="71" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G115" s="26"/>
       <c r="H115" s="26"/>
@@ -37349,7 +37344,7 @@
     <row r="116" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="39"/>
       <c r="B116" s="45" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C116" s="46">
         <f t="shared" si="1"/>
@@ -37360,10 +37355,10 @@
         <v>Fri</v>
       </c>
       <c r="E116" s="72" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F116" s="73" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G116" s="26"/>
       <c r="H116" s="26"/>
@@ -37377,7 +37372,7 @@
     <row r="117" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="39"/>
       <c r="B117" s="39" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C117" s="49">
         <f t="shared" si="1"/>
@@ -37388,10 +37383,10 @@
         <v>Mon</v>
       </c>
       <c r="E117" s="67" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F117" s="68" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="G117" s="26"/>
       <c r="H117" s="26"/>
@@ -37405,7 +37400,7 @@
     <row r="118" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="39"/>
       <c r="B118" s="51" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C118" s="52">
         <f t="shared" si="1"/>
@@ -37416,10 +37411,10 @@
         <v>Wed</v>
       </c>
       <c r="E118" s="80" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F118" s="81" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G118" s="26"/>
       <c r="H118" s="26"/>
@@ -37433,7 +37428,7 @@
     <row r="119" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="39"/>
       <c r="B119" s="45" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C119" s="46">
         <f t="shared" si="1"/>
@@ -37444,10 +37439,10 @@
         <v>Fri</v>
       </c>
       <c r="E119" s="76" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F119" s="77" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G119" s="26"/>
       <c r="H119" s="26"/>
@@ -37461,7 +37456,7 @@
     <row r="120" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="39"/>
       <c r="B120" s="39" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C120" s="49">
         <f t="shared" si="1"/>
@@ -37472,10 +37467,10 @@
         <v>Mon</v>
       </c>
       <c r="E120" s="26" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F120" s="50" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G120" s="26"/>
       <c r="H120" s="26"/>
@@ -37489,7 +37484,7 @@
     <row r="121" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="39"/>
       <c r="B121" s="51" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C121" s="52">
         <f t="shared" si="1"/>
@@ -37500,10 +37495,10 @@
         <v>Wed</v>
       </c>
       <c r="E121" s="53" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="F121" s="54" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G121" s="26"/>
       <c r="H121" s="26"/>
@@ -37517,7 +37512,7 @@
     <row r="122" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="39"/>
       <c r="B122" s="45" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C122" s="46">
         <f t="shared" si="1"/>
@@ -37528,10 +37523,10 @@
         <v>Fri</v>
       </c>
       <c r="E122" s="47" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F122" s="48" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G122" s="26"/>
       <c r="H122" s="26"/>
@@ -37545,7 +37540,7 @@
     <row r="123" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="39"/>
       <c r="B123" s="39" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C123" s="49">
         <f t="shared" si="1"/>
@@ -37556,10 +37551,10 @@
         <v>Mon</v>
       </c>
       <c r="E123" s="26" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="F123" s="50" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G123" s="26"/>
       <c r="H123" s="26"/>
@@ -37573,7 +37568,7 @@
     <row r="124" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="39"/>
       <c r="B124" s="51" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C124" s="52">
         <f t="shared" si="1"/>
@@ -37584,10 +37579,10 @@
         <v>Wed</v>
       </c>
       <c r="E124" s="55" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F124" s="71" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G124" s="26"/>
       <c r="H124" s="26"/>
@@ -37601,7 +37596,7 @@
     <row r="125" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="39"/>
       <c r="B125" s="45" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C125" s="46">
         <f t="shared" si="1"/>
@@ -37612,10 +37607,10 @@
         <v>Fri</v>
       </c>
       <c r="E125" s="72" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F125" s="73" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G125" s="26"/>
       <c r="H125" s="26"/>
@@ -37629,7 +37624,7 @@
     <row r="126" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="39"/>
       <c r="B126" s="39" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C126" s="49">
         <f t="shared" si="1"/>
@@ -37640,10 +37635,10 @@
         <v>Mon</v>
       </c>
       <c r="E126" s="78" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F126" s="79" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="G126" s="26"/>
       <c r="H126" s="26"/>
@@ -37657,7 +37652,7 @@
     <row r="127" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="39"/>
       <c r="B127" s="51" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C127" s="52">
         <f t="shared" si="1"/>
@@ -37668,10 +37663,10 @@
         <v>Wed</v>
       </c>
       <c r="E127" s="80" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F127" s="81" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="G127" s="26"/>
       <c r="H127" s="26"/>
@@ -37685,7 +37680,7 @@
     <row r="128" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="39"/>
       <c r="B128" s="45" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C128" s="46">
         <f t="shared" si="1"/>
@@ -37696,10 +37691,10 @@
         <v>Fri</v>
       </c>
       <c r="E128" s="65" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="F128" s="66" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G128" s="26"/>
       <c r="H128" s="26"/>
@@ -37713,7 +37708,7 @@
     <row r="129" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="39"/>
       <c r="B129" s="39" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C129" s="49">
         <f t="shared" si="1"/>
@@ -37724,10 +37719,10 @@
         <v>Mon</v>
       </c>
       <c r="E129" s="67" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F129" s="68" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G129" s="26"/>
       <c r="H129" s="26"/>
@@ -37741,7 +37736,7 @@
     <row r="130" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="39"/>
       <c r="B130" s="51" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C130" s="52">
         <f t="shared" si="1"/>
@@ -37752,10 +37747,10 @@
         <v>Wed</v>
       </c>
       <c r="E130" s="55" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F130" s="71" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G130" s="26"/>
       <c r="H130" s="26"/>
@@ -37769,7 +37764,7 @@
     <row r="131" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="39"/>
       <c r="B131" s="45" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C131" s="46">
         <f t="shared" si="1"/>
@@ -37780,10 +37775,10 @@
         <v>Fri</v>
       </c>
       <c r="E131" s="72" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F131" s="73" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G131" s="26"/>
       <c r="H131" s="26"/>
@@ -37797,7 +37792,7 @@
     <row r="132" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="39"/>
       <c r="B132" s="39" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C132" s="49">
         <f t="shared" si="1"/>
@@ -37808,10 +37803,10 @@
         <v>Mon</v>
       </c>
       <c r="E132" s="86" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F132" s="96" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G132" s="26"/>
       <c r="H132" s="26"/>
@@ -37825,7 +37820,7 @@
     <row r="133" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="51"/>
       <c r="B133" s="51" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C133" s="52">
         <f t="shared" si="1"/>
@@ -37836,10 +37831,10 @@
         <v>Wed</v>
       </c>
       <c r="E133" s="82" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F133" s="83" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G133" s="26"/>
       <c r="H133" s="26"/>
@@ -37868,13 +37863,13 @@
     </row>
     <row r="135" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="86" t="s">
+        <v>344</v>
+      </c>
+      <c r="B135" s="26" t="s">
+        <v>345</v>
+      </c>
+      <c r="C135" s="26" t="s">
         <v>346</v>
-      </c>
-      <c r="B135" s="26" t="s">
-        <v>347</v>
-      </c>
-      <c r="C135" s="26" t="s">
-        <v>348</v>
       </c>
       <c r="D135" s="26"/>
       <c r="E135" s="26"/>
@@ -37891,10 +37886,10 @@
     <row r="136" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="26"/>
       <c r="B136" s="26" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C136" s="26" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D136" s="26"/>
       <c r="E136" s="26"/>
@@ -37911,10 +37906,10 @@
     <row r="137" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="26"/>
       <c r="B137" s="87" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C137" s="26" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D137" s="26"/>
       <c r="E137" s="26"/>
@@ -37931,10 +37926,10 @@
     <row r="138" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="26"/>
       <c r="B138" s="88" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C138" s="26" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D138" s="26"/>
       <c r="E138" s="26"/>
@@ -37951,10 +37946,10 @@
     <row r="139" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="26"/>
       <c r="B139" s="26" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C139" s="26" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D139" s="26"/>
       <c r="E139" s="26"/>
@@ -37971,10 +37966,10 @@
     <row r="140" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="26"/>
       <c r="B140" s="26" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C140" s="26" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D140" s="26"/>
       <c r="E140" s="26"/>
@@ -37991,10 +37986,10 @@
     <row r="141" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="26"/>
       <c r="B141" s="26" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C141" s="26" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D141" s="26"/>
       <c r="E141" s="26"/>
@@ -38011,10 +38006,10 @@
     <row r="142" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="26"/>
       <c r="B142" s="69" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C142" s="26" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D142" s="26"/>
       <c r="E142" s="26"/>
@@ -38031,10 +38026,10 @@
     <row r="143" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="26"/>
       <c r="B143" s="26" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C143" s="26" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D143" s="26"/>
       <c r="E143" s="26"/>
@@ -38051,10 +38046,10 @@
     <row r="144" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="26"/>
       <c r="B144" s="67" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C144" s="26" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D144" s="26"/>
       <c r="E144" s="26"/>
@@ -38071,10 +38066,10 @@
     <row r="145" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="26"/>
       <c r="B145" s="26" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C145" s="26" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D145" s="26"/>
       <c r="E145" s="26"/>
@@ -38091,10 +38086,10 @@
     <row r="146" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="26"/>
       <c r="B146" s="78" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C146" s="26" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D146" s="26"/>
       <c r="E146" s="26"/>
